--- a/grupos/1BM - Estadisticos 20211.xlsx
+++ b/grupos/1BM - Estadisticos 20211.xlsx
@@ -18,7 +18,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="429" uniqueCount="145">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="324" uniqueCount="145">
   <si>
     <t>Materia</t>
   </si>
@@ -185,15 +185,15 @@
     <t>Rosas Aguilar Claudia Leonor</t>
   </si>
   <si>
+    <t>García Sánchez Magda Bexabe</t>
+  </si>
+  <si>
+    <t>Herrera Serrano Mayra Iliana</t>
+  </si>
+  <si>
     <t>Morales Vallejo Jorge Luis</t>
   </si>
   <si>
-    <t>Herrera Serrano Mayra Iliana</t>
-  </si>
-  <si>
-    <t>García Sánchez Magda Bexabe</t>
-  </si>
-  <si>
     <t>NC</t>
   </si>
   <si>
@@ -215,58 +215,145 @@
     <t>CASTRO</t>
   </si>
   <si>
+    <t>GONZALEZ</t>
+  </si>
+  <si>
+    <t>MEZA</t>
+  </si>
+  <si>
+    <t>MORALES</t>
+  </si>
+  <si>
+    <t>NEPOMUCENO</t>
+  </si>
+  <si>
+    <t>OFICIAL</t>
+  </si>
+  <si>
+    <t>PEREZ</t>
+  </si>
+  <si>
+    <t>TEXOCO</t>
+  </si>
+  <si>
+    <t>ROMERO</t>
+  </si>
+  <si>
+    <t>MARTINEZ</t>
+  </si>
+  <si>
+    <t>TRUJILLO</t>
+  </si>
+  <si>
+    <t>ARELLANO</t>
+  </si>
+  <si>
+    <t>DE JESUS</t>
+  </si>
+  <si>
+    <t>TZOMPAXTLE</t>
+  </si>
+  <si>
+    <t>CONTRERAS</t>
+  </si>
+  <si>
+    <t>PEDRO EVER</t>
+  </si>
+  <si>
+    <t>ANGEL ALDAIR</t>
+  </si>
+  <si>
+    <t>JORGE GUILLERMO</t>
+  </si>
+  <si>
+    <t>LUIS ENRIQUE</t>
+  </si>
+  <si>
+    <t>ANGEL DAVID</t>
+  </si>
+  <si>
+    <t>WENCESLAO</t>
+  </si>
+  <si>
+    <t>ADAHIR</t>
+  </si>
+  <si>
+    <t>CLEMENTE</t>
+  </si>
+  <si>
+    <t>ANGEL DANIEL</t>
+  </si>
+  <si>
+    <t>BERNABE</t>
+  </si>
+  <si>
     <t>CERON</t>
   </si>
   <si>
     <t>CHULIN</t>
   </si>
   <si>
-    <t>GONZALEZ</t>
-  </si>
-  <si>
-    <t>DE JESUS</t>
+    <t>DE LA CRUZ</t>
+  </si>
+  <si>
+    <t>ELVIRA</t>
+  </si>
+  <si>
+    <t>HERRERA</t>
   </si>
   <si>
     <t>LORENZO</t>
   </si>
   <si>
-    <t>MEZA</t>
-  </si>
-  <si>
-    <t>MORALES</t>
-  </si>
-  <si>
-    <t>NEPOMUCENO</t>
-  </si>
-  <si>
-    <t>OFICIAL</t>
-  </si>
-  <si>
     <t>PALOMARES</t>
   </si>
   <si>
-    <t>PEREZ</t>
+    <t>QUIJANO</t>
+  </si>
+  <si>
+    <t>RICO</t>
+  </si>
+  <si>
+    <t>ROSALIANO</t>
+  </si>
+  <si>
+    <t>ROBLES</t>
+  </si>
+  <si>
+    <t>ROSETE</t>
   </si>
   <si>
     <t>RUIZ</t>
   </si>
   <si>
+    <t>SANCHEZ</t>
+  </si>
+  <si>
     <t>VASQUEZ</t>
   </si>
   <si>
-    <t>TEXOCO</t>
-  </si>
-  <si>
-    <t>ROMERO</t>
+    <t>VENTURA</t>
+  </si>
+  <si>
+    <t>XOTLANIHUA</t>
+  </si>
+  <si>
+    <t>DOLORES</t>
+  </si>
+  <si>
+    <t>MIXCOA</t>
+  </si>
+  <si>
+    <t>TEXCAHUA</t>
   </si>
   <si>
     <t>RODRIGUEZ</t>
   </si>
   <si>
-    <t>RICO</t>
-  </si>
-  <si>
-    <t>MARTINEZ</t>
+    <t>DEL ROSARIO</t>
+  </si>
+  <si>
+    <t>AGUILAR</t>
   </si>
   <si>
     <t>MIXCOHUA</t>
@@ -275,34 +362,40 @@
     <t>LOPEZ</t>
   </si>
   <si>
-    <t>TRUJILLO</t>
-  </si>
-  <si>
-    <t>ARELLANO</t>
-  </si>
-  <si>
-    <t>TZOMPAXTLE</t>
-  </si>
-  <si>
     <t>DE LOS SANTOS</t>
   </si>
   <si>
-    <t>CONTRERAS</t>
+    <t>IXMATLAHUA</t>
+  </si>
+  <si>
+    <t>GARCIA</t>
+  </si>
+  <si>
+    <t>HERNANDEZ</t>
   </si>
   <si>
     <t>NAVARRO</t>
   </si>
   <si>
+    <t>ZEPAHUA</t>
+  </si>
+  <si>
     <t>PIEDRAS</t>
   </si>
   <si>
-    <t>PEDRO EVER</t>
-  </si>
-  <si>
-    <t>ANGEL ALDAIR</t>
-  </si>
-  <si>
-    <t>JORGE GUILLERMO</t>
+    <t>ROSALES</t>
+  </si>
+  <si>
+    <t>CUICAHUA</t>
+  </si>
+  <si>
+    <t>MIGUEL ANGEL</t>
+  </si>
+  <si>
+    <t>NEIL</t>
+  </si>
+  <si>
+    <t>IVAN</t>
   </si>
   <si>
     <t>ITZEL</t>
@@ -311,7 +404,13 @@
     <t>CESAR SAID</t>
   </si>
   <si>
-    <t>LUIS ENRIQUE</t>
+    <t>JASIEL</t>
+  </si>
+  <si>
+    <t>JULIO</t>
+  </si>
+  <si>
+    <t>CELSO ALEJANDRO</t>
   </si>
   <si>
     <t>PATRICIO</t>
@@ -320,133 +419,34 @@
     <t>GREGORIO</t>
   </si>
   <si>
-    <t>ANGEL DAVID</t>
-  </si>
-  <si>
-    <t>WENCESLAO</t>
-  </si>
-  <si>
-    <t>ADAHIR</t>
-  </si>
-  <si>
-    <t>CLEMENTE</t>
-  </si>
-  <si>
     <t>JOSE ALEJANDRO</t>
   </si>
   <si>
-    <t>ANGEL DANIEL</t>
+    <t>JUAN PABLO</t>
+  </si>
+  <si>
+    <t>DIEGO HUMBERTO</t>
+  </si>
+  <si>
+    <t>ALEJANDRO</t>
+  </si>
+  <si>
+    <t>SINAI ANTONIO</t>
+  </si>
+  <si>
+    <t>ZURIEL ELIHU</t>
   </si>
   <si>
     <t>JORGE MARIO</t>
   </si>
   <si>
+    <t>ARIEL CHARBEL</t>
+  </si>
+  <si>
+    <t>ISRAEL</t>
+  </si>
+  <si>
     <t>LUIS REY</t>
-  </si>
-  <si>
-    <t>BERNABE</t>
-  </si>
-  <si>
-    <t>DE LA CRUZ</t>
-  </si>
-  <si>
-    <t>ELVIRA</t>
-  </si>
-  <si>
-    <t>HERRERA</t>
-  </si>
-  <si>
-    <t>QUIJANO</t>
-  </si>
-  <si>
-    <t>ROSALIANO</t>
-  </si>
-  <si>
-    <t>ROBLES</t>
-  </si>
-  <si>
-    <t>ROSETE</t>
-  </si>
-  <si>
-    <t>SANCHEZ</t>
-  </si>
-  <si>
-    <t>VENTURA</t>
-  </si>
-  <si>
-    <t>XOTLANIHUA</t>
-  </si>
-  <si>
-    <t>DOLORES</t>
-  </si>
-  <si>
-    <t>MIXCOA</t>
-  </si>
-  <si>
-    <t>TEXCAHUA</t>
-  </si>
-  <si>
-    <t>DEL ROSARIO</t>
-  </si>
-  <si>
-    <t>AGUILAR</t>
-  </si>
-  <si>
-    <t>IXMATLAHUA</t>
-  </si>
-  <si>
-    <t>GARCIA</t>
-  </si>
-  <si>
-    <t>HERNANDEZ</t>
-  </si>
-  <si>
-    <t>ZEPAHUA</t>
-  </si>
-  <si>
-    <t>ROSALES</t>
-  </si>
-  <si>
-    <t>CUICAHUA</t>
-  </si>
-  <si>
-    <t>MIGUEL ANGEL</t>
-  </si>
-  <si>
-    <t>NEIL</t>
-  </si>
-  <si>
-    <t>IVAN</t>
-  </si>
-  <si>
-    <t>JASIEL</t>
-  </si>
-  <si>
-    <t>JULIO</t>
-  </si>
-  <si>
-    <t>CELSO ALEJANDRO</t>
-  </si>
-  <si>
-    <t>JUAN PABLO</t>
-  </si>
-  <si>
-    <t>DIEGO HUMBERTO</t>
-  </si>
-  <si>
-    <t>ALEJANDRO</t>
-  </si>
-  <si>
-    <t>SINAI ANTONIO</t>
-  </si>
-  <si>
-    <t>ZURIEL ELIHU</t>
-  </si>
-  <si>
-    <t>ARIEL CHARBEL</t>
-  </si>
-  <si>
-    <t>ISRAEL</t>
   </si>
   <si>
     <t>GUSTAVO</t>
@@ -959,16 +959,16 @@
         <v>-1</v>
       </c>
       <c r="I4">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="J4">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="K4">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="L4">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="M4">
         <v>-1</v>
@@ -998,10 +998,10 @@
         <v>7</v>
       </c>
       <c r="V4">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="W4">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="X4">
         <v>8</v>
@@ -1021,13 +1021,13 @@
         <v>-1</v>
       </c>
       <c r="D5">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="E5">
         <v>-1</v>
       </c>
       <c r="F5">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="G5">
         <v>5</v>
@@ -1039,7 +1039,7 @@
         <v>-1</v>
       </c>
       <c r="J5">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="K5">
         <v>-1</v>
@@ -1075,13 +1075,13 @@
         <v>-1</v>
       </c>
       <c r="V5">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="W5">
         <v>-1</v>
       </c>
       <c r="X5">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="Y5">
         <v>5</v>
@@ -1113,16 +1113,16 @@
         <v>-1</v>
       </c>
       <c r="I6">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="J6">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="K6">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="L6">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="M6">
         <v>-1</v>
@@ -1158,7 +1158,7 @@
         <v>9</v>
       </c>
       <c r="X6">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="Y6">
         <v>9</v>
@@ -1190,13 +1190,13 @@
         <v>-1</v>
       </c>
       <c r="I7">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="J7">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="K7">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="L7">
         <v>-1</v>
@@ -1226,13 +1226,13 @@
         <v>10</v>
       </c>
       <c r="U7">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="V7">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="W7">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="X7">
         <v>8</v>
@@ -1252,13 +1252,13 @@
         <v>-1</v>
       </c>
       <c r="D8">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="E8">
         <v>8</v>
       </c>
       <c r="F8">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="G8">
         <v>5</v>
@@ -1270,7 +1270,7 @@
         <v>-1</v>
       </c>
       <c r="J8">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="K8">
         <v>-1</v>
@@ -1306,13 +1306,13 @@
         <v>-1</v>
       </c>
       <c r="V8">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="W8">
         <v>8</v>
       </c>
       <c r="X8">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="Y8">
         <v>5</v>
@@ -1326,10 +1326,10 @@
         <v>6</v>
       </c>
       <c r="C9">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="D9">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="E9">
         <v>-1</v>
@@ -1344,10 +1344,10 @@
         <v>-1</v>
       </c>
       <c r="I9">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="J9">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="K9">
         <v>-1</v>
@@ -1380,10 +1380,10 @@
         <v>6</v>
       </c>
       <c r="U9">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="V9">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="W9">
         <v>-1</v>
@@ -1406,7 +1406,7 @@
         <v>8</v>
       </c>
       <c r="D10">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="E10">
         <v>7</v>
@@ -1421,16 +1421,16 @@
         <v>-1</v>
       </c>
       <c r="I10">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="J10">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="K10">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="L10">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="M10">
         <v>-1</v>
@@ -1460,7 +1460,7 @@
         <v>8</v>
       </c>
       <c r="V10">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="W10">
         <v>7</v>
@@ -1480,7 +1480,7 @@
         <v>7</v>
       </c>
       <c r="C11">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="D11">
         <v>6</v>
@@ -1498,13 +1498,13 @@
         <v>-1</v>
       </c>
       <c r="I11">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="J11">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="K11">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="L11">
         <v>-1</v>
@@ -1534,13 +1534,13 @@
         <v>7</v>
       </c>
       <c r="U11">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="V11">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="W11">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="X11">
         <v>6</v>
@@ -1560,13 +1560,13 @@
         <v>6</v>
       </c>
       <c r="D12">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="E12">
         <v>8</v>
       </c>
       <c r="F12">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="G12">
         <v>7</v>
@@ -1575,16 +1575,16 @@
         <v>-1</v>
       </c>
       <c r="I12">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="J12">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="K12">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="L12">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="M12">
         <v>-1</v>
@@ -1614,13 +1614,13 @@
         <v>6</v>
       </c>
       <c r="V12">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="W12">
         <v>8</v>
       </c>
       <c r="X12">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="Y12">
         <v>7</v>
@@ -1652,16 +1652,16 @@
         <v>-1</v>
       </c>
       <c r="I13">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="J13">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="K13">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="L13">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="M13">
         <v>-1</v>
@@ -1694,7 +1694,7 @@
         <v>7</v>
       </c>
       <c r="W13">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="X13">
         <v>8</v>
@@ -1729,16 +1729,16 @@
         <v>-1</v>
       </c>
       <c r="I14">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="J14">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="K14">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="L14">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="M14">
         <v>-1</v>
@@ -1765,16 +1765,16 @@
         <v>8</v>
       </c>
       <c r="U14">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="V14">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="W14">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="X14">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="Y14">
         <v>10</v>
@@ -1791,13 +1791,13 @@
         <v>6</v>
       </c>
       <c r="D15">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="E15">
         <v>-1</v>
       </c>
       <c r="F15">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="G15">
         <v>7</v>
@@ -1806,16 +1806,16 @@
         <v>-1</v>
       </c>
       <c r="I15">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="J15">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="K15">
         <v>-1</v>
       </c>
       <c r="L15">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="M15">
         <v>-1</v>
@@ -1845,13 +1845,13 @@
         <v>6</v>
       </c>
       <c r="V15">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="W15">
         <v>-1</v>
       </c>
       <c r="X15">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="Y15">
         <v>7</v>
@@ -1883,16 +1883,16 @@
         <v>-1</v>
       </c>
       <c r="I16">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="J16">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="K16">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="L16">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="M16">
         <v>-1</v>
@@ -1922,13 +1922,13 @@
         <v>6</v>
       </c>
       <c r="V16">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="W16">
         <v>6</v>
       </c>
       <c r="X16">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="Y16">
         <v>8</v>
@@ -1942,16 +1942,16 @@
         <v>5</v>
       </c>
       <c r="C17">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="D17">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="E17">
         <v>8</v>
       </c>
       <c r="F17">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="G17">
         <v>7</v>
@@ -1960,16 +1960,16 @@
         <v>-1</v>
       </c>
       <c r="I17">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="J17">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="K17">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="L17">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="M17">
         <v>-1</v>
@@ -1996,16 +1996,16 @@
         <v>5</v>
       </c>
       <c r="U17">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="V17">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="W17">
         <v>8</v>
       </c>
       <c r="X17">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="Y17">
         <v>7</v>
@@ -2019,16 +2019,16 @@
         <v>5</v>
       </c>
       <c r="C18">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="D18">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="E18">
         <v>-1</v>
       </c>
       <c r="F18">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="G18">
         <v>5</v>
@@ -2037,10 +2037,10 @@
         <v>-1</v>
       </c>
       <c r="I18">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="J18">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="K18">
         <v>-1</v>
@@ -2073,16 +2073,16 @@
         <v>5</v>
       </c>
       <c r="U18">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="V18">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="W18">
         <v>-1</v>
       </c>
       <c r="X18">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="Y18">
         <v>5</v>
@@ -2114,16 +2114,16 @@
         <v>-1</v>
       </c>
       <c r="I19">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="J19">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="K19">
         <v>-1</v>
       </c>
       <c r="L19">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="M19">
         <v>-1</v>
@@ -2150,7 +2150,7 @@
         <v>6</v>
       </c>
       <c r="U19">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="V19">
         <v>6</v>
@@ -2176,13 +2176,13 @@
         <v>-1</v>
       </c>
       <c r="D20">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="E20">
         <v>-1</v>
       </c>
       <c r="F20">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="G20">
         <v>5</v>
@@ -2194,7 +2194,7 @@
         <v>-1</v>
       </c>
       <c r="J20">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="K20">
         <v>-1</v>
@@ -2230,13 +2230,13 @@
         <v>-1</v>
       </c>
       <c r="V20">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="W20">
         <v>-1</v>
       </c>
       <c r="X20">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="Y20">
         <v>5</v>
@@ -2268,16 +2268,16 @@
         <v>-1</v>
       </c>
       <c r="I21">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="J21">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="K21">
         <v>-1</v>
       </c>
       <c r="L21">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="M21">
         <v>-1</v>
@@ -2307,7 +2307,7 @@
         <v>7</v>
       </c>
       <c r="V21">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="W21">
         <v>-1</v>
@@ -2330,13 +2330,13 @@
         <v>6</v>
       </c>
       <c r="D22">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="E22">
         <v>8</v>
       </c>
       <c r="F22">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="G22">
         <v>5</v>
@@ -2348,10 +2348,10 @@
         <v>-1</v>
       </c>
       <c r="J22">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="K22">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="L22">
         <v>-1</v>
@@ -2384,13 +2384,13 @@
         <v>6</v>
       </c>
       <c r="V22">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="W22">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="X22">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="Y22">
         <v>5</v>
@@ -2407,13 +2407,13 @@
         <v>-1</v>
       </c>
       <c r="D23">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="E23">
         <v>-1</v>
       </c>
       <c r="F23">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="G23">
         <v>5</v>
@@ -2425,7 +2425,7 @@
         <v>-1</v>
       </c>
       <c r="J23">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="K23">
         <v>-1</v>
@@ -2461,13 +2461,13 @@
         <v>-1</v>
       </c>
       <c r="V23">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="W23">
         <v>-1</v>
       </c>
       <c r="X23">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="Y23">
         <v>5</v>
@@ -2499,16 +2499,16 @@
         <v>-1</v>
       </c>
       <c r="I24">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="J24">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="K24">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="L24">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="M24">
         <v>-1</v>
@@ -2535,13 +2535,13 @@
         <v>8</v>
       </c>
       <c r="U24">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="V24">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="W24">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="X24">
         <v>8</v>
@@ -2576,16 +2576,16 @@
         <v>-1</v>
       </c>
       <c r="I25">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="J25">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="K25">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="L25">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="M25">
         <v>-1</v>
@@ -2615,13 +2615,13 @@
         <v>8</v>
       </c>
       <c r="V25">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="W25">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="X25">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="Y25">
         <v>10</v>
@@ -2656,13 +2656,13 @@
         <v>-1</v>
       </c>
       <c r="J26">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="K26">
         <v>-1</v>
       </c>
       <c r="L26">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="M26">
         <v>-1</v>
@@ -2730,16 +2730,16 @@
         <v>-1</v>
       </c>
       <c r="I27">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="J27">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="K27">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="L27">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="M27">
         <v>-1</v>
@@ -2769,10 +2769,10 @@
         <v>9</v>
       </c>
       <c r="V27">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="W27">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="X27">
         <v>9</v>
@@ -2807,16 +2807,16 @@
         <v>-1</v>
       </c>
       <c r="I28">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="J28">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="K28">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="L28">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="M28">
         <v>-1</v>
@@ -2843,13 +2843,13 @@
         <v>6</v>
       </c>
       <c r="U28">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="V28">
         <v>9</v>
       </c>
       <c r="W28">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="X28">
         <v>9</v>
@@ -2869,7 +2869,7 @@
         <v>8</v>
       </c>
       <c r="D29">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="E29">
         <v>6</v>
@@ -2884,16 +2884,16 @@
         <v>-1</v>
       </c>
       <c r="I29">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="J29">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="K29">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="L29">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="M29">
         <v>-1</v>
@@ -2923,10 +2923,10 @@
         <v>8</v>
       </c>
       <c r="V29">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="W29">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="X29">
         <v>6</v>
@@ -2961,16 +2961,16 @@
         <v>-1</v>
       </c>
       <c r="I30">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="J30">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="K30">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="L30">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="M30">
         <v>-1</v>
@@ -2997,16 +2997,16 @@
         <v>9</v>
       </c>
       <c r="U30">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="V30">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="W30">
         <v>9</v>
       </c>
       <c r="X30">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="Y30">
         <v>9</v>
@@ -3038,16 +3038,16 @@
         <v>-1</v>
       </c>
       <c r="I31">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="J31">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="K31">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="L31">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="M31">
         <v>-1</v>
@@ -3074,16 +3074,16 @@
         <v>8</v>
       </c>
       <c r="U31">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="V31">
         <v>9</v>
       </c>
       <c r="W31">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="X31">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="Y31">
         <v>10</v>
@@ -3097,10 +3097,10 @@
         <v>7</v>
       </c>
       <c r="C32">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="D32">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="E32">
         <v>8</v>
@@ -3115,16 +3115,16 @@
         <v>-1</v>
       </c>
       <c r="I32">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="J32">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="K32">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="L32">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="M32">
         <v>-1</v>
@@ -3151,16 +3151,16 @@
         <v>7</v>
       </c>
       <c r="U32">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="V32">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="W32">
         <v>8</v>
       </c>
       <c r="X32">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="Y32">
         <v>5</v>
@@ -3192,10 +3192,10 @@
         <v>-1</v>
       </c>
       <c r="I33">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="J33">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="K33">
         <v>-1</v>
@@ -3228,10 +3228,10 @@
         <v>6</v>
       </c>
       <c r="U33">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="V33">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="W33">
         <v>8</v>
@@ -3269,16 +3269,16 @@
         <v>-1</v>
       </c>
       <c r="I34">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="J34">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="K34">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="L34">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="M34">
         <v>-1</v>
@@ -3311,7 +3311,7 @@
         <v>9</v>
       </c>
       <c r="W34">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="X34">
         <v>9</v>
@@ -3385,22 +3385,22 @@
         <v>18</v>
       </c>
       <c r="E2">
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="F2">
         <v>58.06</v>
       </c>
       <c r="G2">
+        <v>41.94</v>
+      </c>
+      <c r="H2">
+        <v>6.6</v>
+      </c>
+      <c r="I2">
         <v>0</v>
       </c>
-      <c r="H2">
-        <v>7.2</v>
-      </c>
-      <c r="I2">
-        <v>13</v>
-      </c>
       <c r="J2">
-        <v>41.94</v>
+        <v>0</v>
       </c>
     </row>
     <row r="3" spans="1:10">
@@ -3469,7 +3469,7 @@
     </row>
     <row r="5" spans="1:10">
       <c r="A5" t="s">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="B5" t="s">
         <v>55</v>
@@ -3478,25 +3478,25 @@
         <v>31</v>
       </c>
       <c r="D5">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="E5">
         <v>0</v>
       </c>
       <c r="F5">
-        <v>70.97</v>
+        <v>74.19</v>
       </c>
       <c r="G5">
         <v>0</v>
       </c>
       <c r="H5">
-        <v>7.4</v>
+        <v>8.1</v>
       </c>
       <c r="I5">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="J5">
-        <v>29.03</v>
+        <v>25.81</v>
       </c>
     </row>
     <row r="6" spans="1:10">
@@ -3510,30 +3510,30 @@
         <v>31</v>
       </c>
       <c r="D6">
-        <v>22</v>
+        <v>25</v>
       </c>
       <c r="E6">
+        <v>6</v>
+      </c>
+      <c r="F6">
+        <v>80.65000000000001</v>
+      </c>
+      <c r="G6">
+        <v>19.35</v>
+      </c>
+      <c r="H6">
+        <v>7.1</v>
+      </c>
+      <c r="I6">
         <v>0</v>
       </c>
-      <c r="F6">
-        <v>70.97</v>
-      </c>
-      <c r="G6">
+      <c r="J6">
         <v>0</v>
-      </c>
-      <c r="H6">
-        <v>7.4</v>
-      </c>
-      <c r="I6">
-        <v>9</v>
-      </c>
-      <c r="J6">
-        <v>29.03</v>
       </c>
     </row>
     <row r="7" spans="1:10">
       <c r="A7" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="B7" t="s">
         <v>57</v>
@@ -3542,25 +3542,25 @@
         <v>31</v>
       </c>
       <c r="D7">
-        <v>23</v>
+        <v>27</v>
       </c>
       <c r="E7">
         <v>0</v>
       </c>
       <c r="F7">
-        <v>74.19</v>
+        <v>87.09999999999999</v>
       </c>
       <c r="G7">
         <v>0</v>
       </c>
       <c r="H7">
-        <v>7.7</v>
+        <v>7.1</v>
       </c>
       <c r="I7">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="J7">
-        <v>25.81</v>
+        <v>12.9</v>
       </c>
     </row>
   </sheetData>
@@ -3570,7 +3570,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:F40"/>
+  <dimension ref="A1:F13"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="30.7109375" customWidth="1"/>
@@ -3605,16 +3605,16 @@
         <v>62</v>
       </c>
       <c r="C2" t="s">
-        <v>67</v>
+        <v>65</v>
       </c>
       <c r="D2" t="s">
-        <v>92</v>
+        <v>79</v>
       </c>
       <c r="E2" t="s">
         <v>8</v>
       </c>
       <c r="F2" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
     </row>
     <row r="3" spans="1:6">
@@ -3625,93 +3625,93 @@
         <v>62</v>
       </c>
       <c r="C3" t="s">
-        <v>67</v>
+        <v>65</v>
       </c>
       <c r="D3" t="s">
-        <v>92</v>
+        <v>79</v>
       </c>
       <c r="E3" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="F3" t="s">
-        <v>52</v>
+        <v>57</v>
       </c>
     </row>
     <row r="4" spans="1:6">
       <c r="A4">
-        <v>21330051920186</v>
+        <v>21330051920189</v>
       </c>
       <c r="B4" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="C4" t="s">
-        <v>67</v>
+        <v>71</v>
       </c>
       <c r="D4" t="s">
-        <v>92</v>
+        <v>80</v>
       </c>
       <c r="E4" t="s">
         <v>6</v>
       </c>
       <c r="F4" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
     </row>
     <row r="5" spans="1:6">
       <c r="A5">
-        <v>21330051920186</v>
+        <v>21330051920190</v>
       </c>
       <c r="B5" t="s">
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="C5" t="s">
-        <v>67</v>
+        <v>72</v>
       </c>
       <c r="D5" t="s">
-        <v>92</v>
+        <v>81</v>
       </c>
       <c r="E5" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="F5" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
     </row>
     <row r="6" spans="1:6">
       <c r="A6">
-        <v>21330051920189</v>
+        <v>21330051920195</v>
       </c>
       <c r="B6" t="s">
-        <v>63</v>
+        <v>65</v>
       </c>
       <c r="C6" t="s">
-        <v>78</v>
+        <v>73</v>
       </c>
       <c r="D6" t="s">
-        <v>93</v>
+        <v>82</v>
       </c>
       <c r="E6" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="F6" t="s">
-        <v>52</v>
+        <v>55</v>
       </c>
     </row>
     <row r="7" spans="1:6">
       <c r="A7">
-        <v>21330051920189</v>
+        <v>21330051920198</v>
       </c>
       <c r="B7" t="s">
-        <v>63</v>
+        <v>66</v>
       </c>
       <c r="C7" t="s">
-        <v>78</v>
+        <v>74</v>
       </c>
       <c r="D7" t="s">
-        <v>93</v>
+        <v>83</v>
       </c>
       <c r="E7" t="s">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="F7" t="s">
         <v>55</v>
@@ -3719,79 +3719,79 @@
     </row>
     <row r="8" spans="1:6">
       <c r="A8">
-        <v>21330051920189</v>
+        <v>21330051920199</v>
       </c>
       <c r="B8" t="s">
-        <v>63</v>
+        <v>67</v>
       </c>
       <c r="C8" t="s">
-        <v>78</v>
+        <v>75</v>
       </c>
       <c r="D8" t="s">
-        <v>93</v>
+        <v>84</v>
       </c>
       <c r="E8" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="F8" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
     </row>
     <row r="9" spans="1:6">
       <c r="A9">
-        <v>21330051920190</v>
+        <v>21330051920200</v>
       </c>
       <c r="B9" t="s">
-        <v>64</v>
+        <v>68</v>
       </c>
       <c r="C9" t="s">
-        <v>79</v>
+        <v>76</v>
       </c>
       <c r="D9" t="s">
-        <v>94</v>
+        <v>85</v>
       </c>
       <c r="E9" t="s">
         <v>8</v>
       </c>
       <c r="F9" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
     </row>
     <row r="10" spans="1:6">
       <c r="A10">
-        <v>21330051920190</v>
+        <v>21330051920200</v>
       </c>
       <c r="B10" t="s">
-        <v>64</v>
+        <v>68</v>
       </c>
       <c r="C10" t="s">
-        <v>79</v>
+        <v>76</v>
       </c>
       <c r="D10" t="s">
-        <v>94</v>
+        <v>85</v>
       </c>
       <c r="E10" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="F10" t="s">
-        <v>52</v>
+        <v>57</v>
       </c>
     </row>
     <row r="11" spans="1:6">
       <c r="A11">
-        <v>21330051920190</v>
+        <v>21330051920201</v>
       </c>
       <c r="B11" t="s">
-        <v>64</v>
+        <v>69</v>
       </c>
       <c r="C11" t="s">
-        <v>79</v>
+        <v>77</v>
       </c>
       <c r="D11" t="s">
-        <v>94</v>
+        <v>86</v>
       </c>
       <c r="E11" t="s">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="F11" t="s">
         <v>55</v>
@@ -3799,582 +3799,42 @@
     </row>
     <row r="12" spans="1:6">
       <c r="A12">
-        <v>21330051920191</v>
+        <v>21330051920203</v>
       </c>
       <c r="B12" t="s">
-        <v>65</v>
+        <v>70</v>
       </c>
       <c r="C12" t="s">
-        <v>80</v>
+        <v>78</v>
       </c>
       <c r="D12" t="s">
-        <v>95</v>
+        <v>87</v>
       </c>
       <c r="E12" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="F12" t="s">
-        <v>52</v>
+        <v>55</v>
       </c>
     </row>
     <row r="13" spans="1:6">
       <c r="A13">
-        <v>21330051920192</v>
+        <v>21330051920203</v>
       </c>
       <c r="B13" t="s">
-        <v>66</v>
+        <v>70</v>
       </c>
       <c r="C13" t="s">
-        <v>81</v>
+        <v>78</v>
       </c>
       <c r="D13" t="s">
-        <v>96</v>
+        <v>87</v>
       </c>
       <c r="E13" t="s">
         <v>6</v>
       </c>
       <c r="F13" t="s">
-        <v>55</v>
-      </c>
-    </row>
-    <row r="14" spans="1:6">
-      <c r="A14">
-        <v>21330051920195</v>
-      </c>
-      <c r="B14" t="s">
-        <v>67</v>
-      </c>
-      <c r="C14" t="s">
-        <v>82</v>
-      </c>
-      <c r="D14" t="s">
-        <v>97</v>
-      </c>
-      <c r="E14" t="s">
-        <v>8</v>
-      </c>
-      <c r="F14" t="s">
         <v>57</v>
-      </c>
-    </row>
-    <row r="15" spans="1:6">
-      <c r="A15">
-        <v>21330051920195</v>
-      </c>
-      <c r="B15" t="s">
-        <v>67</v>
-      </c>
-      <c r="C15" t="s">
-        <v>82</v>
-      </c>
-      <c r="D15" t="s">
-        <v>97</v>
-      </c>
-      <c r="E15" t="s">
-        <v>7</v>
-      </c>
-      <c r="F15" t="s">
-        <v>52</v>
-      </c>
-    </row>
-    <row r="16" spans="1:6">
-      <c r="A16">
-        <v>21330051920195</v>
-      </c>
-      <c r="B16" t="s">
-        <v>67</v>
-      </c>
-      <c r="C16" t="s">
-        <v>82</v>
-      </c>
-      <c r="D16" t="s">
-        <v>97</v>
-      </c>
-      <c r="E16" t="s">
-        <v>9</v>
-      </c>
-      <c r="F16" t="s">
-        <v>56</v>
-      </c>
-    </row>
-    <row r="17" spans="1:6">
-      <c r="A17">
-        <v>21330051920197</v>
-      </c>
-      <c r="B17" t="s">
-        <v>68</v>
-      </c>
-      <c r="C17" t="s">
-        <v>83</v>
-      </c>
-      <c r="D17" t="s">
-        <v>98</v>
-      </c>
-      <c r="E17" t="s">
-        <v>7</v>
-      </c>
-      <c r="F17" t="s">
-        <v>52</v>
-      </c>
-    </row>
-    <row r="18" spans="1:6">
-      <c r="A18">
-        <v>21330051920197</v>
-      </c>
-      <c r="B18" t="s">
-        <v>68</v>
-      </c>
-      <c r="C18" t="s">
-        <v>83</v>
-      </c>
-      <c r="D18" t="s">
-        <v>98</v>
-      </c>
-      <c r="E18" t="s">
-        <v>9</v>
-      </c>
-      <c r="F18" t="s">
-        <v>56</v>
-      </c>
-    </row>
-    <row r="19" spans="1:6">
-      <c r="A19">
-        <v>21330051920386</v>
-      </c>
-      <c r="B19" t="s">
-        <v>69</v>
-      </c>
-      <c r="C19" t="s">
-        <v>84</v>
-      </c>
-      <c r="D19" t="s">
-        <v>99</v>
-      </c>
-      <c r="E19" t="s">
-        <v>7</v>
-      </c>
-      <c r="F19" t="s">
-        <v>52</v>
-      </c>
-    </row>
-    <row r="20" spans="1:6">
-      <c r="A20">
-        <v>21330051920386</v>
-      </c>
-      <c r="B20" t="s">
-        <v>69</v>
-      </c>
-      <c r="C20" t="s">
-        <v>84</v>
-      </c>
-      <c r="D20" t="s">
-        <v>99</v>
-      </c>
-      <c r="E20" t="s">
-        <v>6</v>
-      </c>
-      <c r="F20" t="s">
-        <v>55</v>
-      </c>
-    </row>
-    <row r="21" spans="1:6">
-      <c r="A21">
-        <v>21330051920386</v>
-      </c>
-      <c r="B21" t="s">
-        <v>69</v>
-      </c>
-      <c r="C21" t="s">
-        <v>84</v>
-      </c>
-      <c r="D21" t="s">
-        <v>99</v>
-      </c>
-      <c r="E21" t="s">
-        <v>9</v>
-      </c>
-      <c r="F21" t="s">
-        <v>56</v>
-      </c>
-    </row>
-    <row r="22" spans="1:6">
-      <c r="A22">
-        <v>21330051920198</v>
-      </c>
-      <c r="B22" t="s">
-        <v>70</v>
-      </c>
-      <c r="C22" t="s">
-        <v>85</v>
-      </c>
-      <c r="D22" t="s">
-        <v>100</v>
-      </c>
-      <c r="E22" t="s">
-        <v>8</v>
-      </c>
-      <c r="F22" t="s">
-        <v>57</v>
-      </c>
-    </row>
-    <row r="23" spans="1:6">
-      <c r="A23">
-        <v>21330051920198</v>
-      </c>
-      <c r="B23" t="s">
-        <v>70</v>
-      </c>
-      <c r="C23" t="s">
-        <v>85</v>
-      </c>
-      <c r="D23" t="s">
-        <v>100</v>
-      </c>
-      <c r="E23" t="s">
-        <v>7</v>
-      </c>
-      <c r="F23" t="s">
-        <v>52</v>
-      </c>
-    </row>
-    <row r="24" spans="1:6">
-      <c r="A24">
-        <v>21330051920198</v>
-      </c>
-      <c r="B24" t="s">
-        <v>70</v>
-      </c>
-      <c r="C24" t="s">
-        <v>85</v>
-      </c>
-      <c r="D24" t="s">
-        <v>100</v>
-      </c>
-      <c r="E24" t="s">
-        <v>6</v>
-      </c>
-      <c r="F24" t="s">
-        <v>55</v>
-      </c>
-    </row>
-    <row r="25" spans="1:6">
-      <c r="A25">
-        <v>21330051920198</v>
-      </c>
-      <c r="B25" t="s">
-        <v>70</v>
-      </c>
-      <c r="C25" t="s">
-        <v>85</v>
-      </c>
-      <c r="D25" t="s">
-        <v>100</v>
-      </c>
-      <c r="E25" t="s">
-        <v>9</v>
-      </c>
-      <c r="F25" t="s">
-        <v>56</v>
-      </c>
-    </row>
-    <row r="26" spans="1:6">
-      <c r="A26">
-        <v>21330051920199</v>
-      </c>
-      <c r="B26" t="s">
-        <v>71</v>
-      </c>
-      <c r="C26" t="s">
-        <v>86</v>
-      </c>
-      <c r="D26" t="s">
-        <v>101</v>
-      </c>
-      <c r="E26" t="s">
-        <v>8</v>
-      </c>
-      <c r="F26" t="s">
-        <v>57</v>
-      </c>
-    </row>
-    <row r="27" spans="1:6">
-      <c r="A27">
-        <v>21330051920200</v>
-      </c>
-      <c r="B27" t="s">
-        <v>72</v>
-      </c>
-      <c r="C27" t="s">
-        <v>68</v>
-      </c>
-      <c r="D27" t="s">
-        <v>102</v>
-      </c>
-      <c r="E27" t="s">
-        <v>8</v>
-      </c>
-      <c r="F27" t="s">
-        <v>57</v>
-      </c>
-    </row>
-    <row r="28" spans="1:6">
-      <c r="A28">
-        <v>21330051920200</v>
-      </c>
-      <c r="B28" t="s">
-        <v>72</v>
-      </c>
-      <c r="C28" t="s">
-        <v>68</v>
-      </c>
-      <c r="D28" t="s">
-        <v>102</v>
-      </c>
-      <c r="E28" t="s">
-        <v>7</v>
-      </c>
-      <c r="F28" t="s">
-        <v>52</v>
-      </c>
-    </row>
-    <row r="29" spans="1:6">
-      <c r="A29">
-        <v>21330051920200</v>
-      </c>
-      <c r="B29" t="s">
-        <v>72</v>
-      </c>
-      <c r="C29" t="s">
-        <v>68</v>
-      </c>
-      <c r="D29" t="s">
-        <v>102</v>
-      </c>
-      <c r="E29" t="s">
-        <v>6</v>
-      </c>
-      <c r="F29" t="s">
-        <v>55</v>
-      </c>
-    </row>
-    <row r="30" spans="1:6">
-      <c r="A30">
-        <v>21330051920200</v>
-      </c>
-      <c r="B30" t="s">
-        <v>72</v>
-      </c>
-      <c r="C30" t="s">
-        <v>68</v>
-      </c>
-      <c r="D30" t="s">
-        <v>102</v>
-      </c>
-      <c r="E30" t="s">
-        <v>9</v>
-      </c>
-      <c r="F30" t="s">
-        <v>56</v>
-      </c>
-    </row>
-    <row r="31" spans="1:6">
-      <c r="A31">
-        <v>21330051920201</v>
-      </c>
-      <c r="B31" t="s">
-        <v>73</v>
-      </c>
-      <c r="C31" t="s">
-        <v>87</v>
-      </c>
-      <c r="D31" t="s">
-        <v>103</v>
-      </c>
-      <c r="E31" t="s">
-        <v>8</v>
-      </c>
-      <c r="F31" t="s">
-        <v>57</v>
-      </c>
-    </row>
-    <row r="32" spans="1:6">
-      <c r="A32">
-        <v>21330051920202</v>
-      </c>
-      <c r="B32" t="s">
-        <v>74</v>
-      </c>
-      <c r="C32" t="s">
-        <v>88</v>
-      </c>
-      <c r="D32" t="s">
-        <v>104</v>
-      </c>
-      <c r="E32" t="s">
-        <v>7</v>
-      </c>
-      <c r="F32" t="s">
-        <v>52</v>
-      </c>
-    </row>
-    <row r="33" spans="1:6">
-      <c r="A33">
-        <v>21330051920202</v>
-      </c>
-      <c r="B33" t="s">
-        <v>74</v>
-      </c>
-      <c r="C33" t="s">
-        <v>88</v>
-      </c>
-      <c r="D33" t="s">
-        <v>104</v>
-      </c>
-      <c r="E33" t="s">
-        <v>9</v>
-      </c>
-      <c r="F33" t="s">
-        <v>56</v>
-      </c>
-    </row>
-    <row r="34" spans="1:6">
-      <c r="A34">
-        <v>21330051920203</v>
-      </c>
-      <c r="B34" t="s">
-        <v>75</v>
-      </c>
-      <c r="C34" t="s">
-        <v>89</v>
-      </c>
-      <c r="D34" t="s">
-        <v>105</v>
-      </c>
-      <c r="E34" t="s">
-        <v>8</v>
-      </c>
-      <c r="F34" t="s">
-        <v>57</v>
-      </c>
-    </row>
-    <row r="35" spans="1:6">
-      <c r="A35">
-        <v>21330051920203</v>
-      </c>
-      <c r="B35" t="s">
-        <v>75</v>
-      </c>
-      <c r="C35" t="s">
-        <v>89</v>
-      </c>
-      <c r="D35" t="s">
-        <v>105</v>
-      </c>
-      <c r="E35" t="s">
-        <v>7</v>
-      </c>
-      <c r="F35" t="s">
-        <v>52</v>
-      </c>
-    </row>
-    <row r="36" spans="1:6">
-      <c r="A36">
-        <v>21330051920203</v>
-      </c>
-      <c r="B36" t="s">
-        <v>75</v>
-      </c>
-      <c r="C36" t="s">
-        <v>89</v>
-      </c>
-      <c r="D36" t="s">
-        <v>105</v>
-      </c>
-      <c r="E36" t="s">
-        <v>6</v>
-      </c>
-      <c r="F36" t="s">
-        <v>55</v>
-      </c>
-    </row>
-    <row r="37" spans="1:6">
-      <c r="A37">
-        <v>21330051920203</v>
-      </c>
-      <c r="B37" t="s">
-        <v>75</v>
-      </c>
-      <c r="C37" t="s">
-        <v>89</v>
-      </c>
-      <c r="D37" t="s">
-        <v>105</v>
-      </c>
-      <c r="E37" t="s">
-        <v>9</v>
-      </c>
-      <c r="F37" t="s">
-        <v>56</v>
-      </c>
-    </row>
-    <row r="38" spans="1:6">
-      <c r="A38">
-        <v>21330051920209</v>
-      </c>
-      <c r="B38" t="s">
-        <v>76</v>
-      </c>
-      <c r="C38" t="s">
-        <v>90</v>
-      </c>
-      <c r="D38" t="s">
-        <v>106</v>
-      </c>
-      <c r="E38" t="s">
-        <v>7</v>
-      </c>
-      <c r="F38" t="s">
-        <v>52</v>
-      </c>
-    </row>
-    <row r="39" spans="1:6">
-      <c r="A39">
-        <v>21330051920212</v>
-      </c>
-      <c r="B39" t="s">
-        <v>77</v>
-      </c>
-      <c r="C39" t="s">
-        <v>91</v>
-      </c>
-      <c r="D39" t="s">
-        <v>107</v>
-      </c>
-      <c r="E39" t="s">
-        <v>7</v>
-      </c>
-      <c r="F39" t="s">
-        <v>52</v>
-      </c>
-    </row>
-    <row r="40" spans="1:6">
-      <c r="A40">
-        <v>21330051920212</v>
-      </c>
-      <c r="B40" t="s">
-        <v>77</v>
-      </c>
-      <c r="C40" t="s">
-        <v>91</v>
-      </c>
-      <c r="D40" t="s">
-        <v>107</v>
-      </c>
-      <c r="E40" t="s">
-        <v>6</v>
-      </c>
-      <c r="F40" t="s">
-        <v>55</v>
       </c>
     </row>
   </sheetData>
@@ -4416,279 +3876,279 @@
         <v>62</v>
       </c>
       <c r="C2" t="s">
-        <v>67</v>
+        <v>65</v>
       </c>
       <c r="D2" t="s">
-        <v>92</v>
+        <v>79</v>
       </c>
       <c r="E2">
-        <v>4</v>
+        <v>2</v>
       </c>
     </row>
     <row r="3" spans="1:5">
       <c r="A3">
-        <v>21330051920198</v>
+        <v>21330051920200</v>
       </c>
       <c r="B3" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="C3" t="s">
+        <v>76</v>
+      </c>
+      <c r="D3" t="s">
         <v>85</v>
       </c>
-      <c r="D3" t="s">
-        <v>100</v>
-      </c>
       <c r="E3">
-        <v>4</v>
+        <v>2</v>
       </c>
     </row>
     <row r="4" spans="1:5">
       <c r="A4">
-        <v>21330051920200</v>
+        <v>21330051920203</v>
       </c>
       <c r="B4" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="C4" t="s">
-        <v>68</v>
+        <v>78</v>
       </c>
       <c r="D4" t="s">
-        <v>102</v>
+        <v>87</v>
       </c>
       <c r="E4">
-        <v>4</v>
+        <v>2</v>
       </c>
     </row>
     <row r="5" spans="1:5">
       <c r="A5">
-        <v>21330051920203</v>
+        <v>21330051920189</v>
       </c>
       <c r="B5" t="s">
-        <v>75</v>
+        <v>63</v>
       </c>
       <c r="C5" t="s">
-        <v>89</v>
+        <v>71</v>
       </c>
       <c r="D5" t="s">
-        <v>105</v>
+        <v>80</v>
       </c>
       <c r="E5">
-        <v>4</v>
+        <v>1</v>
       </c>
     </row>
     <row r="6" spans="1:5">
       <c r="A6">
-        <v>21330051920189</v>
+        <v>21330051920190</v>
       </c>
       <c r="B6" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="C6" t="s">
-        <v>78</v>
+        <v>72</v>
       </c>
       <c r="D6" t="s">
-        <v>93</v>
+        <v>81</v>
       </c>
       <c r="E6">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="7" spans="1:5">
       <c r="A7">
-        <v>21330051920190</v>
+        <v>21330051920195</v>
       </c>
       <c r="B7" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="C7" t="s">
-        <v>79</v>
+        <v>73</v>
       </c>
       <c r="D7" t="s">
-        <v>94</v>
+        <v>82</v>
       </c>
       <c r="E7">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="8" spans="1:5">
       <c r="A8">
-        <v>21330051920195</v>
+        <v>21330051920198</v>
       </c>
       <c r="B8" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="C8" t="s">
-        <v>82</v>
+        <v>74</v>
       </c>
       <c r="D8" t="s">
-        <v>97</v>
+        <v>83</v>
       </c>
       <c r="E8">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="9" spans="1:5">
       <c r="A9">
-        <v>21330051920386</v>
+        <v>21330051920199</v>
       </c>
       <c r="B9" t="s">
-        <v>69</v>
+        <v>67</v>
       </c>
       <c r="C9" t="s">
+        <v>75</v>
+      </c>
+      <c r="D9" t="s">
         <v>84</v>
       </c>
-      <c r="D9" t="s">
-        <v>99</v>
-      </c>
       <c r="E9">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="10" spans="1:5">
       <c r="A10">
-        <v>21330051920197</v>
+        <v>21330051920201</v>
       </c>
       <c r="B10" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="C10" t="s">
-        <v>83</v>
+        <v>77</v>
       </c>
       <c r="D10" t="s">
-        <v>98</v>
+        <v>86</v>
       </c>
       <c r="E10">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="11" spans="1:5">
       <c r="A11">
-        <v>21330051920202</v>
+        <v>21330051920185</v>
       </c>
       <c r="B11" t="s">
-        <v>74</v>
+        <v>62</v>
       </c>
       <c r="C11" t="s">
-        <v>88</v>
+        <v>106</v>
       </c>
       <c r="D11" t="s">
-        <v>104</v>
+        <v>123</v>
       </c>
       <c r="E11">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="12" spans="1:5">
       <c r="A12">
-        <v>21330051920212</v>
+        <v>21330051920187</v>
       </c>
       <c r="B12" t="s">
-        <v>77</v>
+        <v>88</v>
       </c>
       <c r="C12" t="s">
-        <v>91</v>
+        <v>107</v>
       </c>
       <c r="D12" t="s">
-        <v>107</v>
+        <v>124</v>
       </c>
       <c r="E12">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="13" spans="1:5">
       <c r="A13">
-        <v>21330051920191</v>
+        <v>21330051920188</v>
       </c>
       <c r="B13" t="s">
-        <v>65</v>
+        <v>88</v>
       </c>
       <c r="C13" t="s">
-        <v>80</v>
+        <v>108</v>
       </c>
       <c r="D13" t="s">
-        <v>95</v>
+        <v>125</v>
       </c>
       <c r="E13">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="14" spans="1:5">
       <c r="A14">
-        <v>21330051920192</v>
+        <v>21330051920191</v>
       </c>
       <c r="B14" t="s">
-        <v>66</v>
+        <v>89</v>
       </c>
       <c r="C14" t="s">
-        <v>81</v>
+        <v>109</v>
       </c>
       <c r="D14" t="s">
-        <v>96</v>
+        <v>126</v>
       </c>
       <c r="E14">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="15" spans="1:5">
       <c r="A15">
-        <v>21330051920199</v>
+        <v>21330051920192</v>
       </c>
       <c r="B15" t="s">
-        <v>71</v>
+        <v>90</v>
       </c>
       <c r="C15" t="s">
-        <v>86</v>
+        <v>97</v>
       </c>
       <c r="D15" t="s">
-        <v>101</v>
+        <v>127</v>
       </c>
       <c r="E15">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="16" spans="1:5">
       <c r="A16">
-        <v>21330051920201</v>
+        <v>21330051920193</v>
       </c>
       <c r="B16" t="s">
-        <v>73</v>
+        <v>91</v>
       </c>
       <c r="C16" t="s">
-        <v>87</v>
+        <v>110</v>
       </c>
       <c r="D16" t="s">
-        <v>103</v>
+        <v>128</v>
       </c>
       <c r="E16">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="17" spans="1:5">
       <c r="A17">
-        <v>21330051920209</v>
+        <v>21330051920194</v>
       </c>
       <c r="B17" t="s">
-        <v>76</v>
+        <v>92</v>
       </c>
       <c r="C17" t="s">
-        <v>90</v>
+        <v>111</v>
       </c>
       <c r="D17" t="s">
-        <v>106</v>
+        <v>129</v>
       </c>
       <c r="E17">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="18" spans="1:5">
       <c r="A18">
-        <v>21330051920185</v>
+        <v>21330051920196</v>
       </c>
       <c r="B18" t="s">
-        <v>62</v>
+        <v>93</v>
       </c>
       <c r="C18" t="s">
-        <v>119</v>
+        <v>105</v>
       </c>
       <c r="D18" t="s">
         <v>130</v>
@@ -4699,13 +4159,13 @@
     </row>
     <row r="19" spans="1:5">
       <c r="A19">
-        <v>21330051920187</v>
+        <v>21330051920197</v>
       </c>
       <c r="B19" t="s">
-        <v>108</v>
+        <v>76</v>
       </c>
       <c r="C19" t="s">
-        <v>120</v>
+        <v>112</v>
       </c>
       <c r="D19" t="s">
         <v>131</v>
@@ -4716,13 +4176,13 @@
     </row>
     <row r="20" spans="1:5">
       <c r="A20">
-        <v>21330051920188</v>
+        <v>21330051920386</v>
       </c>
       <c r="B20" t="s">
-        <v>108</v>
+        <v>94</v>
       </c>
       <c r="C20" t="s">
-        <v>121</v>
+        <v>113</v>
       </c>
       <c r="D20" t="s">
         <v>132</v>
@@ -4733,13 +4193,13 @@
     </row>
     <row r="21" spans="1:5">
       <c r="A21">
-        <v>21330051920193</v>
+        <v>21330051920202</v>
       </c>
       <c r="B21" t="s">
-        <v>109</v>
+        <v>95</v>
       </c>
       <c r="C21" t="s">
-        <v>122</v>
+        <v>114</v>
       </c>
       <c r="D21" t="s">
         <v>133</v>
@@ -4750,13 +4210,13 @@
     </row>
     <row r="22" spans="1:5">
       <c r="A22">
-        <v>21330051920194</v>
+        <v>21330051920204</v>
       </c>
       <c r="B22" t="s">
-        <v>110</v>
+        <v>96</v>
       </c>
       <c r="C22" t="s">
-        <v>123</v>
+        <v>115</v>
       </c>
       <c r="D22" t="s">
         <v>134</v>
@@ -4767,13 +4227,13 @@
     </row>
     <row r="23" spans="1:5">
       <c r="A23">
-        <v>21330051920196</v>
+        <v>21330051920205</v>
       </c>
       <c r="B23" t="s">
-        <v>111</v>
+        <v>97</v>
       </c>
       <c r="C23" t="s">
-        <v>118</v>
+        <v>116</v>
       </c>
       <c r="D23" t="s">
         <v>135</v>
@@ -4784,13 +4244,13 @@
     </row>
     <row r="24" spans="1:5">
       <c r="A24">
-        <v>21330051920204</v>
+        <v>21330051920206</v>
       </c>
       <c r="B24" t="s">
-        <v>112</v>
+        <v>98</v>
       </c>
       <c r="C24" t="s">
-        <v>124</v>
+        <v>117</v>
       </c>
       <c r="D24" t="s">
         <v>136</v>
@@ -4801,13 +4261,13 @@
     </row>
     <row r="25" spans="1:5">
       <c r="A25">
-        <v>21330051920205</v>
+        <v>21330051920207</v>
       </c>
       <c r="B25" t="s">
-        <v>81</v>
+        <v>99</v>
       </c>
       <c r="C25" t="s">
-        <v>125</v>
+        <v>102</v>
       </c>
       <c r="D25" t="s">
         <v>137</v>
@@ -4818,13 +4278,13 @@
     </row>
     <row r="26" spans="1:5">
       <c r="A26">
-        <v>21330051920206</v>
+        <v>21330051920208</v>
       </c>
       <c r="B26" t="s">
-        <v>113</v>
+        <v>100</v>
       </c>
       <c r="C26" t="s">
-        <v>126</v>
+        <v>71</v>
       </c>
       <c r="D26" t="s">
         <v>138</v>
@@ -4835,13 +4295,13 @@
     </row>
     <row r="27" spans="1:5">
       <c r="A27">
-        <v>21330051920207</v>
+        <v>21330051920209</v>
       </c>
       <c r="B27" t="s">
-        <v>114</v>
+        <v>101</v>
       </c>
       <c r="C27" t="s">
-        <v>116</v>
+        <v>118</v>
       </c>
       <c r="D27" t="s">
         <v>139</v>
@@ -4852,13 +4312,13 @@
     </row>
     <row r="28" spans="1:5">
       <c r="A28">
-        <v>21330051920208</v>
+        <v>21330051920210</v>
       </c>
       <c r="B28" t="s">
-        <v>115</v>
+        <v>102</v>
       </c>
       <c r="C28" t="s">
-        <v>78</v>
+        <v>119</v>
       </c>
       <c r="D28" t="s">
         <v>140</v>
@@ -4869,13 +4329,13 @@
     </row>
     <row r="29" spans="1:5">
       <c r="A29">
-        <v>21330051920210</v>
+        <v>21330051920211</v>
       </c>
       <c r="B29" t="s">
-        <v>116</v>
+        <v>74</v>
       </c>
       <c r="C29" t="s">
-        <v>127</v>
+        <v>109</v>
       </c>
       <c r="D29" t="s">
         <v>141</v>
@@ -4886,13 +4346,13 @@
     </row>
     <row r="30" spans="1:5">
       <c r="A30">
-        <v>21330051920211</v>
+        <v>21330051920212</v>
       </c>
       <c r="B30" t="s">
-        <v>85</v>
+        <v>103</v>
       </c>
       <c r="C30" t="s">
-        <v>80</v>
+        <v>120</v>
       </c>
       <c r="D30" t="s">
         <v>142</v>
@@ -4906,10 +4366,10 @@
         <v>21330051920213</v>
       </c>
       <c r="B31" t="s">
-        <v>117</v>
+        <v>104</v>
       </c>
       <c r="C31" t="s">
-        <v>128</v>
+        <v>121</v>
       </c>
       <c r="D31" t="s">
         <v>143</v>
@@ -4923,10 +4383,10 @@
         <v>21330051920214</v>
       </c>
       <c r="B32" t="s">
-        <v>118</v>
+        <v>105</v>
       </c>
       <c r="C32" t="s">
-        <v>129</v>
+        <v>122</v>
       </c>
       <c r="D32" t="s">
         <v>144</v>
@@ -4942,7 +4402,7 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G9"/>
+  <dimension ref="A1:G15"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="30.7109375" customWidth="1"/>
@@ -4974,16 +4434,16 @@
     </row>
     <row r="2" spans="1:7">
       <c r="A2">
-        <v>21330051920201</v>
+        <v>21330051920197</v>
       </c>
       <c r="B2" t="s">
-        <v>73</v>
+        <v>76</v>
       </c>
       <c r="C2" t="s">
-        <v>87</v>
+        <v>112</v>
       </c>
       <c r="D2" t="s">
-        <v>103</v>
+        <v>131</v>
       </c>
       <c r="E2" t="s">
         <v>5</v>
@@ -4997,131 +4457,131 @@
     </row>
     <row r="3" spans="1:7">
       <c r="A3">
-        <v>21330051920201</v>
+        <v>21330051920197</v>
       </c>
       <c r="B3" t="s">
-        <v>73</v>
+        <v>76</v>
       </c>
       <c r="C3" t="s">
-        <v>87</v>
+        <v>112</v>
       </c>
       <c r="D3" t="s">
-        <v>103</v>
+        <v>131</v>
       </c>
       <c r="E3" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="F3" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="G3">
-        <v>-1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="4" spans="1:7">
       <c r="A4">
-        <v>21330051920191</v>
+        <v>21330051920386</v>
       </c>
       <c r="B4" t="s">
-        <v>65</v>
+        <v>94</v>
       </c>
       <c r="C4" t="s">
-        <v>80</v>
+        <v>113</v>
       </c>
       <c r="D4" t="s">
-        <v>95</v>
+        <v>132</v>
       </c>
       <c r="E4" t="s">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="F4" t="s">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="G4">
-        <v>-1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="5" spans="1:7">
       <c r="A5">
-        <v>21330051920192</v>
+        <v>21330051920386</v>
       </c>
       <c r="B5" t="s">
-        <v>66</v>
+        <v>94</v>
       </c>
       <c r="C5" t="s">
-        <v>81</v>
+        <v>113</v>
       </c>
       <c r="D5" t="s">
-        <v>96</v>
+        <v>132</v>
       </c>
       <c r="E5" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="F5" t="s">
-        <v>55</v>
+        <v>52</v>
       </c>
       <c r="G5">
-        <v>-1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="6" spans="1:7">
       <c r="A6">
-        <v>21330051920199</v>
+        <v>21330051920201</v>
       </c>
       <c r="B6" t="s">
-        <v>71</v>
+        <v>69</v>
       </c>
       <c r="C6" t="s">
+        <v>77</v>
+      </c>
+      <c r="D6" t="s">
         <v>86</v>
       </c>
-      <c r="D6" t="s">
-        <v>101</v>
-      </c>
       <c r="E6" t="s">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="F6" t="s">
-        <v>57</v>
+        <v>54</v>
       </c>
       <c r="G6">
-        <v>-1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="7" spans="1:7">
       <c r="A7">
-        <v>21330051920207</v>
+        <v>21330051920201</v>
       </c>
       <c r="B7" t="s">
-        <v>114</v>
+        <v>69</v>
       </c>
       <c r="C7" t="s">
-        <v>116</v>
+        <v>77</v>
       </c>
       <c r="D7" t="s">
-        <v>139</v>
+        <v>86</v>
       </c>
       <c r="E7" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="F7" t="s">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="G7">
-        <v>5</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="8" spans="1:7">
       <c r="A8">
-        <v>21330051920209</v>
+        <v>21330051920212</v>
       </c>
       <c r="B8" t="s">
-        <v>76</v>
+        <v>103</v>
       </c>
       <c r="C8" t="s">
-        <v>90</v>
+        <v>120</v>
       </c>
       <c r="D8" t="s">
-        <v>106</v>
+        <v>142</v>
       </c>
       <c r="E8" t="s">
         <v>7</v>
@@ -5130,21 +4590,21 @@
         <v>52</v>
       </c>
       <c r="G8">
-        <v>-1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="9" spans="1:7">
       <c r="A9">
-        <v>21330051920213</v>
+        <v>21330051920212</v>
       </c>
       <c r="B9" t="s">
-        <v>117</v>
+        <v>103</v>
       </c>
       <c r="C9" t="s">
-        <v>128</v>
+        <v>120</v>
       </c>
       <c r="D9" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="E9" t="s">
         <v>10</v>
@@ -5153,6 +4613,144 @@
         <v>53</v>
       </c>
       <c r="G9">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="10" spans="1:7">
+      <c r="A10">
+        <v>21330051920213</v>
+      </c>
+      <c r="B10" t="s">
+        <v>104</v>
+      </c>
+      <c r="C10" t="s">
+        <v>121</v>
+      </c>
+      <c r="D10" t="s">
+        <v>143</v>
+      </c>
+      <c r="E10" t="s">
+        <v>7</v>
+      </c>
+      <c r="F10" t="s">
+        <v>52</v>
+      </c>
+      <c r="G10">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="11" spans="1:7">
+      <c r="A11">
+        <v>21330051920213</v>
+      </c>
+      <c r="B11" t="s">
+        <v>104</v>
+      </c>
+      <c r="C11" t="s">
+        <v>121</v>
+      </c>
+      <c r="D11" t="s">
+        <v>143</v>
+      </c>
+      <c r="E11" t="s">
+        <v>10</v>
+      </c>
+      <c r="F11" t="s">
+        <v>53</v>
+      </c>
+      <c r="G11">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="12" spans="1:7">
+      <c r="A12">
+        <v>21330051920192</v>
+      </c>
+      <c r="B12" t="s">
+        <v>90</v>
+      </c>
+      <c r="C12" t="s">
+        <v>97</v>
+      </c>
+      <c r="D12" t="s">
+        <v>127</v>
+      </c>
+      <c r="E12" t="s">
+        <v>7</v>
+      </c>
+      <c r="F12" t="s">
+        <v>52</v>
+      </c>
+      <c r="G12">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="13" spans="1:7">
+      <c r="A13">
+        <v>21330051920199</v>
+      </c>
+      <c r="B13" t="s">
+        <v>67</v>
+      </c>
+      <c r="C13" t="s">
+        <v>75</v>
+      </c>
+      <c r="D13" t="s">
+        <v>84</v>
+      </c>
+      <c r="E13" t="s">
+        <v>8</v>
+      </c>
+      <c r="F13" t="s">
+        <v>55</v>
+      </c>
+      <c r="G13">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="14" spans="1:7">
+      <c r="A14">
+        <v>21330051920207</v>
+      </c>
+      <c r="B14" t="s">
+        <v>99</v>
+      </c>
+      <c r="C14" t="s">
+        <v>102</v>
+      </c>
+      <c r="D14" t="s">
+        <v>137</v>
+      </c>
+      <c r="E14" t="s">
+        <v>10</v>
+      </c>
+      <c r="F14" t="s">
+        <v>53</v>
+      </c>
+      <c r="G14">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="15" spans="1:7">
+      <c r="A15">
+        <v>21330051920209</v>
+      </c>
+      <c r="B15" t="s">
+        <v>101</v>
+      </c>
+      <c r="C15" t="s">
+        <v>118</v>
+      </c>
+      <c r="D15" t="s">
+        <v>139</v>
+      </c>
+      <c r="E15" t="s">
+        <v>7</v>
+      </c>
+      <c r="F15" t="s">
+        <v>52</v>
+      </c>
+      <c r="G15">
         <v>5</v>
       </c>
     </row>

--- a/grupos/1BM - Estadisticos 20211.xlsx
+++ b/grupos/1BM - Estadisticos 20211.xlsx
@@ -18,7 +18,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="324" uniqueCount="145">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="304" uniqueCount="145">
   <si>
     <t>Materia</t>
   </si>
@@ -179,13 +179,13 @@
     <t>Ochoa Martínez Mayeli</t>
   </si>
   <si>
+    <t>Rosas Aguilar Claudia Leonor</t>
+  </si>
+  <si>
+    <t>García Sánchez Magda Bexabe</t>
+  </si>
+  <si>
     <t>Velasco Sánchez David</t>
-  </si>
-  <si>
-    <t>Rosas Aguilar Claudia Leonor</t>
-  </si>
-  <si>
-    <t>García Sánchez Magda Bexabe</t>
   </si>
   <si>
     <t>Herrera Serrano Mayra Iliana</t>
@@ -956,7 +956,7 @@
         <v>8</v>
       </c>
       <c r="H4">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="I4">
         <v>7</v>
@@ -971,7 +971,7 @@
         <v>8</v>
       </c>
       <c r="M4">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="N4">
         <v>-1</v>
@@ -992,7 +992,7 @@
         <v>-1</v>
       </c>
       <c r="T4">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="U4">
         <v>7</v>
@@ -1007,7 +1007,7 @@
         <v>8</v>
       </c>
       <c r="Y4">
-        <v>8</v>
+        <v>9</v>
       </c>
     </row>
     <row r="5" spans="1:25">
@@ -1033,7 +1033,7 @@
         <v>5</v>
       </c>
       <c r="H5">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="I5">
         <v>-1</v>
@@ -1048,7 +1048,7 @@
         <v>-1</v>
       </c>
       <c r="M5">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="N5">
         <v>-1</v>
@@ -1110,7 +1110,7 @@
         <v>9</v>
       </c>
       <c r="H6">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="I6">
         <v>7</v>
@@ -1125,7 +1125,7 @@
         <v>9</v>
       </c>
       <c r="M6">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="N6">
         <v>-1</v>
@@ -1146,7 +1146,7 @@
         <v>-1</v>
       </c>
       <c r="T6">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="U6">
         <v>8</v>
@@ -1161,7 +1161,7 @@
         <v>8</v>
       </c>
       <c r="Y6">
-        <v>9</v>
+        <v>10</v>
       </c>
     </row>
     <row r="7" spans="1:25">
@@ -1187,7 +1187,7 @@
         <v>6</v>
       </c>
       <c r="H7">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="I7">
         <v>6</v>
@@ -1202,7 +1202,7 @@
         <v>-1</v>
       </c>
       <c r="M7">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="N7">
         <v>-1</v>
@@ -1264,7 +1264,7 @@
         <v>5</v>
       </c>
       <c r="H8">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="I8">
         <v>-1</v>
@@ -1279,7 +1279,7 @@
         <v>-1</v>
       </c>
       <c r="M8">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="N8">
         <v>-1</v>
@@ -1341,7 +1341,7 @@
         <v>5</v>
       </c>
       <c r="H9">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="I9">
         <v>6</v>
@@ -1356,7 +1356,7 @@
         <v>-1</v>
       </c>
       <c r="M9">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="N9">
         <v>-1</v>
@@ -1377,7 +1377,7 @@
         <v>-1</v>
       </c>
       <c r="T9">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="U9">
         <v>6</v>
@@ -1418,7 +1418,7 @@
         <v>6</v>
       </c>
       <c r="H10">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="I10">
         <v>7</v>
@@ -1433,7 +1433,7 @@
         <v>7</v>
       </c>
       <c r="M10">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="N10">
         <v>-1</v>
@@ -1469,7 +1469,7 @@
         <v>8</v>
       </c>
       <c r="Y10">
-        <v>6</v>
+        <v>8</v>
       </c>
     </row>
     <row r="11" spans="1:25">
@@ -1495,7 +1495,7 @@
         <v>9</v>
       </c>
       <c r="H11">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="I11">
         <v>6</v>
@@ -1510,7 +1510,7 @@
         <v>-1</v>
       </c>
       <c r="M11">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="N11">
         <v>-1</v>
@@ -1572,7 +1572,7 @@
         <v>7</v>
       </c>
       <c r="H12">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="I12">
         <v>6</v>
@@ -1587,7 +1587,7 @@
         <v>6</v>
       </c>
       <c r="M12">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="N12">
         <v>-1</v>
@@ -1649,7 +1649,7 @@
         <v>9</v>
       </c>
       <c r="H13">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="I13">
         <v>6</v>
@@ -1664,7 +1664,7 @@
         <v>7</v>
       </c>
       <c r="M13">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="N13">
         <v>-1</v>
@@ -1726,7 +1726,7 @@
         <v>10</v>
       </c>
       <c r="H14">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="I14">
         <v>8</v>
@@ -1741,7 +1741,7 @@
         <v>9</v>
       </c>
       <c r="M14">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="N14">
         <v>-1</v>
@@ -1762,7 +1762,7 @@
         <v>-1</v>
       </c>
       <c r="T14">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="U14">
         <v>7</v>
@@ -1803,7 +1803,7 @@
         <v>7</v>
       </c>
       <c r="H15">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="I15">
         <v>6</v>
@@ -1818,7 +1818,7 @@
         <v>6</v>
       </c>
       <c r="M15">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="N15">
         <v>-1</v>
@@ -1854,7 +1854,7 @@
         <v>6</v>
       </c>
       <c r="Y15">
-        <v>7</v>
+        <v>8</v>
       </c>
     </row>
     <row r="16" spans="1:25">
@@ -1880,7 +1880,7 @@
         <v>8</v>
       </c>
       <c r="H16">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="I16">
         <v>6</v>
@@ -1895,7 +1895,7 @@
         <v>9</v>
       </c>
       <c r="M16">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="N16">
         <v>-1</v>
@@ -1931,7 +1931,7 @@
         <v>8</v>
       </c>
       <c r="Y16">
-        <v>8</v>
+        <v>9</v>
       </c>
     </row>
     <row r="17" spans="1:25">
@@ -1957,7 +1957,7 @@
         <v>7</v>
       </c>
       <c r="H17">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="I17">
         <v>6</v>
@@ -1972,7 +1972,7 @@
         <v>6</v>
       </c>
       <c r="M17">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="N17">
         <v>-1</v>
@@ -2034,7 +2034,7 @@
         <v>5</v>
       </c>
       <c r="H18">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="I18">
         <v>7</v>
@@ -2049,7 +2049,7 @@
         <v>-1</v>
       </c>
       <c r="M18">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="N18">
         <v>-1</v>
@@ -2111,7 +2111,7 @@
         <v>8</v>
       </c>
       <c r="H19">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="I19">
         <v>7</v>
@@ -2126,7 +2126,7 @@
         <v>6</v>
       </c>
       <c r="M19">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="N19">
         <v>-1</v>
@@ -2162,7 +2162,7 @@
         <v>6</v>
       </c>
       <c r="Y19">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="20" spans="1:25">
@@ -2188,7 +2188,7 @@
         <v>5</v>
       </c>
       <c r="H20">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="I20">
         <v>-1</v>
@@ -2203,7 +2203,7 @@
         <v>-1</v>
       </c>
       <c r="M20">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="N20">
         <v>-1</v>
@@ -2265,7 +2265,7 @@
         <v>7</v>
       </c>
       <c r="H21">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="I21">
         <v>6</v>
@@ -2280,7 +2280,7 @@
         <v>6</v>
       </c>
       <c r="M21">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="N21">
         <v>-1</v>
@@ -2342,7 +2342,7 @@
         <v>5</v>
       </c>
       <c r="H22">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="I22">
         <v>-1</v>
@@ -2357,7 +2357,7 @@
         <v>-1</v>
       </c>
       <c r="M22">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="N22">
         <v>-1</v>
@@ -2419,7 +2419,7 @@
         <v>5</v>
       </c>
       <c r="H23">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="I23">
         <v>-1</v>
@@ -2434,7 +2434,7 @@
         <v>-1</v>
       </c>
       <c r="M23">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="N23">
         <v>-1</v>
@@ -2496,7 +2496,7 @@
         <v>10</v>
       </c>
       <c r="H24">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="I24">
         <v>7</v>
@@ -2511,7 +2511,7 @@
         <v>7</v>
       </c>
       <c r="M24">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="N24">
         <v>-1</v>
@@ -2532,7 +2532,7 @@
         <v>-1</v>
       </c>
       <c r="T24">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="U24">
         <v>7</v>
@@ -2573,7 +2573,7 @@
         <v>10</v>
       </c>
       <c r="H25">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="I25">
         <v>7</v>
@@ -2588,7 +2588,7 @@
         <v>9</v>
       </c>
       <c r="M25">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="N25">
         <v>-1</v>
@@ -2609,7 +2609,7 @@
         <v>-1</v>
       </c>
       <c r="T25">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="U25">
         <v>8</v>
@@ -2650,7 +2650,7 @@
         <v>5</v>
       </c>
       <c r="H26">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="I26">
         <v>-1</v>
@@ -2665,7 +2665,7 @@
         <v>7</v>
       </c>
       <c r="M26">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="N26">
         <v>-1</v>
@@ -2686,7 +2686,7 @@
         <v>-1</v>
       </c>
       <c r="T26">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="U26">
         <v>6</v>
@@ -2701,7 +2701,7 @@
         <v>8</v>
       </c>
       <c r="Y26">
-        <v>5</v>
+        <v>7</v>
       </c>
     </row>
     <row r="27" spans="1:25">
@@ -2727,7 +2727,7 @@
         <v>9</v>
       </c>
       <c r="H27">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="I27">
         <v>9</v>
@@ -2742,7 +2742,7 @@
         <v>9</v>
       </c>
       <c r="M27">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="N27">
         <v>-1</v>
@@ -2763,7 +2763,7 @@
         <v>-1</v>
       </c>
       <c r="T27">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="U27">
         <v>9</v>
@@ -2778,7 +2778,7 @@
         <v>9</v>
       </c>
       <c r="Y27">
-        <v>9</v>
+        <v>10</v>
       </c>
     </row>
     <row r="28" spans="1:25">
@@ -2804,7 +2804,7 @@
         <v>9</v>
       </c>
       <c r="H28">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="I28">
         <v>7</v>
@@ -2819,7 +2819,7 @@
         <v>8</v>
       </c>
       <c r="M28">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="N28">
         <v>-1</v>
@@ -2881,7 +2881,7 @@
         <v>10</v>
       </c>
       <c r="H29">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="I29">
         <v>7</v>
@@ -2896,7 +2896,7 @@
         <v>6</v>
       </c>
       <c r="M29">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="N29">
         <v>-1</v>
@@ -2958,7 +2958,7 @@
         <v>9</v>
       </c>
       <c r="H30">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="I30">
         <v>9</v>
@@ -2973,7 +2973,7 @@
         <v>8</v>
       </c>
       <c r="M30">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="N30">
         <v>-1</v>
@@ -3009,7 +3009,7 @@
         <v>8</v>
       </c>
       <c r="Y30">
-        <v>9</v>
+        <v>10</v>
       </c>
     </row>
     <row r="31" spans="1:25">
@@ -3035,7 +3035,7 @@
         <v>10</v>
       </c>
       <c r="H31">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="I31">
         <v>6</v>
@@ -3050,7 +3050,7 @@
         <v>10</v>
       </c>
       <c r="M31">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="N31">
         <v>-1</v>
@@ -3112,7 +3112,7 @@
         <v>5</v>
       </c>
       <c r="H32">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="I32">
         <v>6</v>
@@ -3127,7 +3127,7 @@
         <v>8</v>
       </c>
       <c r="M32">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="N32">
         <v>-1</v>
@@ -3163,7 +3163,7 @@
         <v>8</v>
       </c>
       <c r="Y32">
-        <v>5</v>
+        <v>8</v>
       </c>
     </row>
     <row r="33" spans="1:25">
@@ -3189,7 +3189,7 @@
         <v>5</v>
       </c>
       <c r="H33">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="I33">
         <v>6</v>
@@ -3204,7 +3204,7 @@
         <v>-1</v>
       </c>
       <c r="M33">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="N33">
         <v>-1</v>
@@ -3225,7 +3225,7 @@
         <v>-1</v>
       </c>
       <c r="T33">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="U33">
         <v>7</v>
@@ -3266,7 +3266,7 @@
         <v>9</v>
       </c>
       <c r="H34">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="I34">
         <v>9</v>
@@ -3281,7 +3281,7 @@
         <v>8</v>
       </c>
       <c r="M34">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="N34">
         <v>-1</v>
@@ -3317,7 +3317,7 @@
         <v>9</v>
       </c>
       <c r="Y34">
-        <v>9</v>
+        <v>10</v>
       </c>
     </row>
   </sheetData>
@@ -3405,7 +3405,7 @@
     </row>
     <row r="3" spans="1:10">
       <c r="A3" t="s">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="B3" t="s">
         <v>53</v>
@@ -3414,19 +3414,19 @@
         <v>31</v>
       </c>
       <c r="D3">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="E3">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="F3">
-        <v>67.73999999999999</v>
+        <v>64.52</v>
       </c>
       <c r="G3">
-        <v>32.26</v>
+        <v>35.48</v>
       </c>
       <c r="H3">
-        <v>7.3</v>
+        <v>6.6</v>
       </c>
       <c r="I3">
         <v>0</v>
@@ -3437,7 +3437,7 @@
     </row>
     <row r="4" spans="1:10">
       <c r="A4" t="s">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="B4" t="s">
         <v>54</v>
@@ -3446,30 +3446,30 @@
         <v>31</v>
       </c>
       <c r="D4">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="E4">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="F4">
-        <v>70.97</v>
+        <v>74.19</v>
       </c>
       <c r="G4">
-        <v>29.03</v>
+        <v>0</v>
       </c>
       <c r="H4">
-        <v>6.6</v>
+        <v>8.1</v>
       </c>
       <c r="I4">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="J4">
-        <v>0</v>
+        <v>25.81</v>
       </c>
     </row>
     <row r="5" spans="1:10">
       <c r="A5" t="s">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="B5" t="s">
         <v>55</v>
@@ -3481,22 +3481,22 @@
         <v>23</v>
       </c>
       <c r="E5">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="F5">
         <v>74.19</v>
       </c>
       <c r="G5">
+        <v>25.81</v>
+      </c>
+      <c r="H5">
+        <v>7.7</v>
+      </c>
+      <c r="I5">
         <v>0</v>
       </c>
-      <c r="H5">
-        <v>8.1</v>
-      </c>
-      <c r="I5">
-        <v>8</v>
-      </c>
       <c r="J5">
-        <v>25.81</v>
+        <v>0</v>
       </c>
     </row>
     <row r="6" spans="1:10">
@@ -3614,7 +3614,7 @@
         <v>8</v>
       </c>
       <c r="F2" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
     </row>
     <row r="3" spans="1:6">
@@ -3674,7 +3674,7 @@
         <v>8</v>
       </c>
       <c r="F5" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
     </row>
     <row r="6" spans="1:6">
@@ -3694,7 +3694,7 @@
         <v>8</v>
       </c>
       <c r="F6" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
     </row>
     <row r="7" spans="1:6">
@@ -3714,7 +3714,7 @@
         <v>8</v>
       </c>
       <c r="F7" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
     </row>
     <row r="8" spans="1:6">
@@ -3734,7 +3734,7 @@
         <v>8</v>
       </c>
       <c r="F8" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
     </row>
     <row r="9" spans="1:6">
@@ -3754,7 +3754,7 @@
         <v>8</v>
       </c>
       <c r="F9" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
     </row>
     <row r="10" spans="1:6">
@@ -3794,7 +3794,7 @@
         <v>8</v>
       </c>
       <c r="F11" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
     </row>
     <row r="12" spans="1:6">
@@ -3814,7 +3814,7 @@
         <v>8</v>
       </c>
       <c r="F12" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
     </row>
     <row r="13" spans="1:6">
@@ -4402,7 +4402,7 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G15"/>
+  <dimension ref="A1:G11"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="30.7109375" customWidth="1"/>
@@ -4449,7 +4449,7 @@
         <v>5</v>
       </c>
       <c r="F2" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="G2">
         <v>5</v>
@@ -4495,7 +4495,7 @@
         <v>5</v>
       </c>
       <c r="F4" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="G4">
         <v>5</v>
@@ -4541,7 +4541,7 @@
         <v>5</v>
       </c>
       <c r="F6" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="G6">
         <v>5</v>
@@ -4564,7 +4564,7 @@
         <v>8</v>
       </c>
       <c r="F7" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="G7">
         <v>-1</v>
@@ -4572,16 +4572,16 @@
     </row>
     <row r="8" spans="1:7">
       <c r="A8">
-        <v>21330051920212</v>
+        <v>21330051920192</v>
       </c>
       <c r="B8" t="s">
-        <v>103</v>
+        <v>90</v>
       </c>
       <c r="C8" t="s">
-        <v>120</v>
+        <v>97</v>
       </c>
       <c r="D8" t="s">
-        <v>142</v>
+        <v>127</v>
       </c>
       <c r="E8" t="s">
         <v>7</v>
@@ -4595,39 +4595,39 @@
     </row>
     <row r="9" spans="1:7">
       <c r="A9">
-        <v>21330051920212</v>
+        <v>21330051920199</v>
       </c>
       <c r="B9" t="s">
-        <v>103</v>
+        <v>67</v>
       </c>
       <c r="C9" t="s">
-        <v>120</v>
+        <v>75</v>
       </c>
       <c r="D9" t="s">
-        <v>142</v>
+        <v>84</v>
       </c>
       <c r="E9" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="F9" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="G9">
-        <v>5</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="10" spans="1:7">
       <c r="A10">
-        <v>21330051920213</v>
+        <v>21330051920209</v>
       </c>
       <c r="B10" t="s">
-        <v>104</v>
+        <v>101</v>
       </c>
       <c r="C10" t="s">
-        <v>121</v>
+        <v>118</v>
       </c>
       <c r="D10" t="s">
-        <v>143</v>
+        <v>139</v>
       </c>
       <c r="E10" t="s">
         <v>7</v>
@@ -4641,116 +4641,24 @@
     </row>
     <row r="11" spans="1:7">
       <c r="A11">
-        <v>21330051920213</v>
+        <v>21330051920212</v>
       </c>
       <c r="B11" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="C11" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="D11" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="E11" t="s">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="F11" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="G11">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="12" spans="1:7">
-      <c r="A12">
-        <v>21330051920192</v>
-      </c>
-      <c r="B12" t="s">
-        <v>90</v>
-      </c>
-      <c r="C12" t="s">
-        <v>97</v>
-      </c>
-      <c r="D12" t="s">
-        <v>127</v>
-      </c>
-      <c r="E12" t="s">
-        <v>7</v>
-      </c>
-      <c r="F12" t="s">
-        <v>52</v>
-      </c>
-      <c r="G12">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="13" spans="1:7">
-      <c r="A13">
-        <v>21330051920199</v>
-      </c>
-      <c r="B13" t="s">
-        <v>67</v>
-      </c>
-      <c r="C13" t="s">
-        <v>75</v>
-      </c>
-      <c r="D13" t="s">
-        <v>84</v>
-      </c>
-      <c r="E13" t="s">
-        <v>8</v>
-      </c>
-      <c r="F13" t="s">
-        <v>55</v>
-      </c>
-      <c r="G13">
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="14" spans="1:7">
-      <c r="A14">
-        <v>21330051920207</v>
-      </c>
-      <c r="B14" t="s">
-        <v>99</v>
-      </c>
-      <c r="C14" t="s">
-        <v>102</v>
-      </c>
-      <c r="D14" t="s">
-        <v>137</v>
-      </c>
-      <c r="E14" t="s">
-        <v>10</v>
-      </c>
-      <c r="F14" t="s">
-        <v>53</v>
-      </c>
-      <c r="G14">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="15" spans="1:7">
-      <c r="A15">
-        <v>21330051920209</v>
-      </c>
-      <c r="B15" t="s">
-        <v>101</v>
-      </c>
-      <c r="C15" t="s">
-        <v>118</v>
-      </c>
-      <c r="D15" t="s">
-        <v>139</v>
-      </c>
-      <c r="E15" t="s">
-        <v>7</v>
-      </c>
-      <c r="F15" t="s">
-        <v>52</v>
-      </c>
-      <c r="G15">
         <v>5</v>
       </c>
     </row>

--- a/grupos/1BM - Estadisticos 20211.xlsx
+++ b/grupos/1BM - Estadisticos 20211.xlsx
@@ -1045,7 +1045,7 @@
         <v>-1</v>
       </c>
       <c r="L5">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="M5">
         <v>6</v>
@@ -1276,7 +1276,7 @@
         <v>-1</v>
       </c>
       <c r="L8">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="M8">
         <v>5</v>
@@ -1353,7 +1353,7 @@
         <v>-1</v>
       </c>
       <c r="L9">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="M9">
         <v>6</v>
@@ -2046,7 +2046,7 @@
         <v>-1</v>
       </c>
       <c r="L18">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="M18">
         <v>5</v>
@@ -2200,7 +2200,7 @@
         <v>-1</v>
       </c>
       <c r="L20">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="M20">
         <v>5</v>
@@ -2354,7 +2354,7 @@
         <v>6</v>
       </c>
       <c r="L22">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="M22">
         <v>5</v>
@@ -2431,7 +2431,7 @@
         <v>-1</v>
       </c>
       <c r="L23">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="M23">
         <v>5</v>
@@ -3201,7 +3201,7 @@
         <v>-1</v>
       </c>
       <c r="L33">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="M33">
         <v>5</v>
@@ -3237,7 +3237,7 @@
         <v>8</v>
       </c>
       <c r="X33">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="Y33">
         <v>5</v>
@@ -3510,19 +3510,19 @@
         <v>31</v>
       </c>
       <c r="D6">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="E6">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="F6">
-        <v>80.65000000000001</v>
+        <v>77.42</v>
       </c>
       <c r="G6">
-        <v>19.35</v>
+        <v>22.58</v>
       </c>
       <c r="H6">
-        <v>7.1</v>
+        <v>7</v>
       </c>
       <c r="I6">
         <v>0</v>

--- a/grupos/1BM - Estadisticos 20211.xlsx
+++ b/grupos/1BM - Estadisticos 20211.xlsx
@@ -18,7 +18,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="304" uniqueCount="145">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="228" uniqueCount="148">
   <si>
     <t>Materia</t>
   </si>
@@ -86,6 +86,9 @@
     <t>DE LA CRUZ DEL ROSARIO JASIEL</t>
   </si>
   <si>
+    <t>DE LA CRUZ TZOPITL JOSE MANUEL</t>
+  </si>
+  <si>
     <t>ELVIRA AGUILAR JULIO</t>
   </si>
   <si>
@@ -179,21 +182,21 @@
     <t>Ochoa Martínez Mayeli</t>
   </si>
   <si>
+    <t>Velasco Sánchez David</t>
+  </si>
+  <si>
     <t>Rosas Aguilar Claudia Leonor</t>
   </si>
   <si>
+    <t>Morales Vallejo Jorge Luis</t>
+  </si>
+  <si>
     <t>García Sánchez Magda Bexabe</t>
   </si>
   <si>
-    <t>Velasco Sánchez David</t>
-  </si>
-  <si>
     <t>Herrera Serrano Mayra Iliana</t>
   </si>
   <si>
-    <t>Morales Vallejo Jorge Luis</t>
-  </si>
-  <si>
     <t>NC</t>
   </si>
   <si>
@@ -209,15 +212,39 @@
     <t>ALVAREZ</t>
   </si>
   <si>
+    <t>BERNABE</t>
+  </si>
+  <si>
     <t>BONILLA</t>
   </si>
   <si>
     <t>CASTRO</t>
   </si>
   <si>
+    <t>CERON</t>
+  </si>
+  <si>
+    <t>CHULIN</t>
+  </si>
+  <si>
+    <t>DE LA CRUZ</t>
+  </si>
+  <si>
+    <t>ELVIRA</t>
+  </si>
+  <si>
     <t>GONZALEZ</t>
   </si>
   <si>
+    <t>HERRERA</t>
+  </si>
+  <si>
+    <t>DE JESUS</t>
+  </si>
+  <si>
+    <t>LORENZO</t>
+  </si>
+  <si>
     <t>MEZA</t>
   </si>
   <si>
@@ -230,45 +257,162 @@
     <t>OFICIAL</t>
   </si>
   <si>
+    <t>PALOMARES</t>
+  </si>
+  <si>
     <t>PEREZ</t>
   </si>
   <si>
+    <t>QUIJANO</t>
+  </si>
+  <si>
+    <t>RICO</t>
+  </si>
+  <si>
+    <t>ROSALIANO</t>
+  </si>
+  <si>
+    <t>ROBLES</t>
+  </si>
+  <si>
+    <t>ROSETE</t>
+  </si>
+  <si>
+    <t>RUIZ</t>
+  </si>
+  <si>
+    <t>SANCHEZ</t>
+  </si>
+  <si>
+    <t>TRUJILLO</t>
+  </si>
+  <si>
+    <t>VASQUEZ</t>
+  </si>
+  <si>
+    <t>VENTURA</t>
+  </si>
+  <si>
+    <t>XOTLANIHUA</t>
+  </si>
+  <si>
+    <t>DOLORES</t>
+  </si>
+  <si>
+    <t>MIXCOA</t>
+  </si>
+  <si>
+    <t>TEXCAHUA</t>
+  </si>
+  <si>
     <t>TEXOCO</t>
   </si>
   <si>
     <t>ROMERO</t>
   </si>
   <si>
+    <t>RODRIGUEZ</t>
+  </si>
+  <si>
+    <t>DEL ROSARIO</t>
+  </si>
+  <si>
+    <t>TZOPITL</t>
+  </si>
+  <si>
+    <t>AGUILAR</t>
+  </si>
+  <si>
     <t>MARTINEZ</t>
   </si>
   <si>
-    <t>TRUJILLO</t>
+    <t>MIXCOHUA</t>
+  </si>
+  <si>
+    <t>LOPEZ</t>
   </si>
   <si>
     <t>ARELLANO</t>
   </si>
   <si>
-    <t>DE JESUS</t>
-  </si>
-  <si>
     <t>TZOMPAXTLE</t>
   </si>
   <si>
+    <t>DE LOS SANTOS</t>
+  </si>
+  <si>
     <t>CONTRERAS</t>
   </si>
   <si>
+    <t>IXMATLAHUA</t>
+  </si>
+  <si>
+    <t>GARCIA</t>
+  </si>
+  <si>
+    <t>HERNANDEZ</t>
+  </si>
+  <si>
+    <t>NAVARRO</t>
+  </si>
+  <si>
+    <t>ZEPAHUA</t>
+  </si>
+  <si>
+    <t>PIEDRAS</t>
+  </si>
+  <si>
+    <t>ROSALES</t>
+  </si>
+  <si>
+    <t>CUICAHUA</t>
+  </si>
+  <si>
+    <t>MIGUEL ANGEL</t>
+  </si>
+  <si>
     <t>PEDRO EVER</t>
   </si>
   <si>
+    <t>NEIL</t>
+  </si>
+  <si>
+    <t>IVAN</t>
+  </si>
+  <si>
     <t>ANGEL ALDAIR</t>
   </si>
   <si>
     <t>JORGE GUILLERMO</t>
   </si>
   <si>
+    <t>ITZEL</t>
+  </si>
+  <si>
+    <t>CESAR SAID</t>
+  </si>
+  <si>
+    <t>JASIEL</t>
+  </si>
+  <si>
+    <t>JOSE MANUEL</t>
+  </si>
+  <si>
+    <t>JULIO</t>
+  </si>
+  <si>
     <t>LUIS ENRIQUE</t>
   </si>
   <si>
+    <t>CELSO ALEJANDRO</t>
+  </si>
+  <si>
+    <t>PATRICIO</t>
+  </si>
+  <si>
+    <t>GREGORIO</t>
+  </si>
+  <si>
     <t>ANGEL DAVID</t>
   </si>
   <si>
@@ -281,145 +425,10 @@
     <t>CLEMENTE</t>
   </si>
   <si>
+    <t>JOSE ALEJANDRO</t>
+  </si>
+  <si>
     <t>ANGEL DANIEL</t>
-  </si>
-  <si>
-    <t>BERNABE</t>
-  </si>
-  <si>
-    <t>CERON</t>
-  </si>
-  <si>
-    <t>CHULIN</t>
-  </si>
-  <si>
-    <t>DE LA CRUZ</t>
-  </si>
-  <si>
-    <t>ELVIRA</t>
-  </si>
-  <si>
-    <t>HERRERA</t>
-  </si>
-  <si>
-    <t>LORENZO</t>
-  </si>
-  <si>
-    <t>PALOMARES</t>
-  </si>
-  <si>
-    <t>QUIJANO</t>
-  </si>
-  <si>
-    <t>RICO</t>
-  </si>
-  <si>
-    <t>ROSALIANO</t>
-  </si>
-  <si>
-    <t>ROBLES</t>
-  </si>
-  <si>
-    <t>ROSETE</t>
-  </si>
-  <si>
-    <t>RUIZ</t>
-  </si>
-  <si>
-    <t>SANCHEZ</t>
-  </si>
-  <si>
-    <t>VASQUEZ</t>
-  </si>
-  <si>
-    <t>VENTURA</t>
-  </si>
-  <si>
-    <t>XOTLANIHUA</t>
-  </si>
-  <si>
-    <t>DOLORES</t>
-  </si>
-  <si>
-    <t>MIXCOA</t>
-  </si>
-  <si>
-    <t>TEXCAHUA</t>
-  </si>
-  <si>
-    <t>RODRIGUEZ</t>
-  </si>
-  <si>
-    <t>DEL ROSARIO</t>
-  </si>
-  <si>
-    <t>AGUILAR</t>
-  </si>
-  <si>
-    <t>MIXCOHUA</t>
-  </si>
-  <si>
-    <t>LOPEZ</t>
-  </si>
-  <si>
-    <t>DE LOS SANTOS</t>
-  </si>
-  <si>
-    <t>IXMATLAHUA</t>
-  </si>
-  <si>
-    <t>GARCIA</t>
-  </si>
-  <si>
-    <t>HERNANDEZ</t>
-  </si>
-  <si>
-    <t>NAVARRO</t>
-  </si>
-  <si>
-    <t>ZEPAHUA</t>
-  </si>
-  <si>
-    <t>PIEDRAS</t>
-  </si>
-  <si>
-    <t>ROSALES</t>
-  </si>
-  <si>
-    <t>CUICAHUA</t>
-  </si>
-  <si>
-    <t>MIGUEL ANGEL</t>
-  </si>
-  <si>
-    <t>NEIL</t>
-  </si>
-  <si>
-    <t>IVAN</t>
-  </si>
-  <si>
-    <t>ITZEL</t>
-  </si>
-  <si>
-    <t>CESAR SAID</t>
-  </si>
-  <si>
-    <t>JASIEL</t>
-  </si>
-  <si>
-    <t>JULIO</t>
-  </si>
-  <si>
-    <t>CELSO ALEJANDRO</t>
-  </si>
-  <si>
-    <t>PATRICIO</t>
-  </si>
-  <si>
-    <t>GREGORIO</t>
-  </si>
-  <si>
-    <t>JOSE ALEJANDRO</t>
   </si>
   <si>
     <t>JUAN PABLO</t>
@@ -810,7 +819,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:Y34"/>
+  <dimension ref="A1:Y35"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="50.7109375" customWidth="1"/>
@@ -974,25 +983,25 @@
         <v>9</v>
       </c>
       <c r="N4">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="O4">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="P4">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="Q4">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="R4">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="S4">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="T4">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="U4">
         <v>7</v>
@@ -1018,13 +1027,13 @@
         <v>5</v>
       </c>
       <c r="C5">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="D5">
         <v>5</v>
       </c>
       <c r="E5">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="F5">
         <v>5</v>
@@ -1036,13 +1045,13 @@
         <v>5</v>
       </c>
       <c r="I5">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="J5">
         <v>5</v>
       </c>
       <c r="K5">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="L5">
         <v>6</v>
@@ -1051,37 +1060,37 @@
         <v>6</v>
       </c>
       <c r="N5">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="O5">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="P5">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="Q5">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="R5">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="S5">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="T5">
         <v>5</v>
       </c>
       <c r="U5">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="V5">
         <v>5</v>
       </c>
       <c r="W5">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="X5">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="Y5">
         <v>5</v>
@@ -1128,22 +1137,22 @@
         <v>10</v>
       </c>
       <c r="N6">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="O6">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="P6">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="Q6">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="R6">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="S6">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="T6">
         <v>9</v>
@@ -1199,46 +1208,46 @@
         <v>9</v>
       </c>
       <c r="L7">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="M7">
         <v>6</v>
       </c>
       <c r="N7">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="O7">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="P7">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="Q7">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="R7">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="S7">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="T7">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="U7">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="V7">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="W7">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="X7">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="Y7">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="8" spans="1:25">
@@ -1249,7 +1258,7 @@
         <v>5</v>
       </c>
       <c r="C8">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="D8">
         <v>5</v>
@@ -1267,13 +1276,13 @@
         <v>5</v>
       </c>
       <c r="I8">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="J8">
         <v>5</v>
       </c>
       <c r="K8">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="L8">
         <v>6</v>
@@ -1282,40 +1291,40 @@
         <v>5</v>
       </c>
       <c r="N8">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="O8">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="P8">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="Q8">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="R8">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="S8">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="T8">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="U8">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="V8">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="W8">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="X8">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="Y8">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="9" spans="1:25">
@@ -1332,7 +1341,7 @@
         <v>5</v>
       </c>
       <c r="E9">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="F9">
         <v>7</v>
@@ -1350,7 +1359,7 @@
         <v>6</v>
       </c>
       <c r="K9">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="L9">
         <v>6</v>
@@ -1359,40 +1368,40 @@
         <v>6</v>
       </c>
       <c r="N9">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="O9">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="P9">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="Q9">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="R9">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="S9">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="T9">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="U9">
         <v>6</v>
       </c>
       <c r="V9">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="W9">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="X9">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="Y9">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="10" spans="1:25">
@@ -1436,22 +1445,22 @@
         <v>10</v>
       </c>
       <c r="N10">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="O10">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="P10">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="Q10">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="R10">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="S10">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="T10">
         <v>6</v>
@@ -1460,13 +1469,13 @@
         <v>8</v>
       </c>
       <c r="V10">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="W10">
         <v>7</v>
       </c>
       <c r="X10">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="Y10">
         <v>8</v>
@@ -1507,43 +1516,43 @@
         <v>7</v>
       </c>
       <c r="L11">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="M11">
         <v>8</v>
       </c>
       <c r="N11">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="O11">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="P11">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="Q11">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="R11">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="S11">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="T11">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="U11">
         <v>6</v>
       </c>
       <c r="V11">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="W11">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="X11">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="Y11">
         <v>9</v>
@@ -1590,37 +1599,37 @@
         <v>7</v>
       </c>
       <c r="N12">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="O12">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="P12">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="Q12">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="R12">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="S12">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="T12">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="U12">
         <v>6</v>
       </c>
       <c r="V12">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="W12">
         <v>8</v>
       </c>
       <c r="X12">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="Y12">
         <v>7</v>
@@ -1667,22 +1676,22 @@
         <v>9</v>
       </c>
       <c r="N13">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="O13">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="P13">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="Q13">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="R13">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="S13">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="T13">
         <v>6</v>
@@ -1691,93 +1700,57 @@
         <v>6</v>
       </c>
       <c r="V13">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="W13">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="X13">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="Y13">
-        <v>9</v>
+        <v>8</v>
       </c>
     </row>
     <row r="14" spans="1:25">
       <c r="A14" s="1" t="s">
         <v>22</v>
       </c>
-      <c r="B14">
-        <v>8</v>
-      </c>
       <c r="C14">
         <v>6</v>
       </c>
       <c r="D14">
-        <v>6</v>
-      </c>
-      <c r="E14">
-        <v>7</v>
-      </c>
-      <c r="F14">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="G14">
-        <v>10</v>
-      </c>
-      <c r="H14">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="I14">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="J14">
-        <v>8</v>
-      </c>
-      <c r="K14">
-        <v>9</v>
-      </c>
-      <c r="L14">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="M14">
-        <v>10</v>
-      </c>
-      <c r="N14">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="O14">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="P14">
-        <v>-1</v>
-      </c>
-      <c r="Q14">
-        <v>-1</v>
-      </c>
-      <c r="R14">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="S14">
-        <v>-1</v>
-      </c>
-      <c r="T14">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="U14">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="V14">
-        <v>7</v>
-      </c>
-      <c r="W14">
-        <v>8</v>
-      </c>
-      <c r="X14">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="Y14">
-        <v>10</v>
+        <v>6</v>
       </c>
     </row>
     <row r="15" spans="1:25">
@@ -1785,76 +1758,76 @@
         <v>23</v>
       </c>
       <c r="B15">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="C15">
         <v>6</v>
       </c>
       <c r="D15">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="E15">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="F15">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="G15">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="H15">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="I15">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="J15">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="K15">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="L15">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="M15">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="N15">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="O15">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="P15">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="Q15">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="R15">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="S15">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="T15">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="U15">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="V15">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="W15">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="X15">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="Y15">
-        <v>8</v>
+        <v>10</v>
       </c>
     </row>
     <row r="16" spans="1:25">
@@ -1862,13 +1835,13 @@
         <v>24</v>
       </c>
       <c r="B16">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="C16">
         <v>6</v>
       </c>
       <c r="D16">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="E16">
         <v>6</v>
@@ -1877,61 +1850,61 @@
         <v>6</v>
       </c>
       <c r="G16">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="H16">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="I16">
         <v>6</v>
       </c>
       <c r="J16">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="K16">
         <v>6</v>
       </c>
       <c r="L16">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="M16">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="N16">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="O16">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="P16">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="Q16">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="R16">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="S16">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="T16">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="U16">
         <v>6</v>
       </c>
       <c r="V16">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="W16">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="X16">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="Y16">
-        <v>9</v>
+        <v>7</v>
       </c>
     </row>
     <row r="17" spans="1:25">
@@ -1939,76 +1912,76 @@
         <v>25</v>
       </c>
       <c r="B17">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="C17">
         <v>6</v>
       </c>
       <c r="D17">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="E17">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="F17">
         <v>6</v>
       </c>
       <c r="G17">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="H17">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="I17">
         <v>6</v>
       </c>
       <c r="J17">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="K17">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="L17">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="M17">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="N17">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="O17">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="P17">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="Q17">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="R17">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="S17">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="T17">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="U17">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="V17">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="W17">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="X17">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="Y17">
-        <v>7</v>
+        <v>8</v>
       </c>
     </row>
     <row r="18" spans="1:25">
@@ -2025,67 +1998,67 @@
         <v>5</v>
       </c>
       <c r="E18">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="F18">
         <v>6</v>
       </c>
       <c r="G18">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="H18">
         <v>5</v>
       </c>
       <c r="I18">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="J18">
         <v>5</v>
       </c>
       <c r="K18">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="L18">
         <v>6</v>
       </c>
       <c r="M18">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="N18">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="O18">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="P18">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="Q18">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="R18">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="S18">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="T18">
         <v>5</v>
       </c>
       <c r="U18">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="V18">
         <v>5</v>
       </c>
       <c r="W18">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="X18">
         <v>6</v>
       </c>
       <c r="Y18">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="19" spans="1:25">
@@ -2093,76 +2066,76 @@
         <v>27</v>
       </c>
       <c r="B19">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C19">
         <v>6</v>
       </c>
       <c r="D19">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="E19">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="F19">
         <v>6</v>
       </c>
       <c r="G19">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="H19">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="I19">
         <v>7</v>
       </c>
       <c r="J19">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="K19">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="L19">
         <v>6</v>
       </c>
       <c r="M19">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="N19">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="O19">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="P19">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="Q19">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="R19">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="S19">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="T19">
         <v>6</v>
       </c>
       <c r="U19">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="V19">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="W19">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="X19">
         <v>6</v>
       </c>
       <c r="Y19">
-        <v>7</v>
+        <v>5</v>
       </c>
     </row>
     <row r="20" spans="1:25">
@@ -2170,76 +2143,76 @@
         <v>28</v>
       </c>
       <c r="B20">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="C20">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="D20">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="E20">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="F20">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="G20">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="H20">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="I20">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="J20">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="K20">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="L20">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="M20">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="N20">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="O20">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="P20">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="Q20">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="R20">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="S20">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="T20">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="U20">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="V20">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="W20">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="X20">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="Y20">
-        <v>5</v>
+        <v>7</v>
       </c>
     </row>
     <row r="21" spans="1:25">
@@ -2250,73 +2223,73 @@
         <v>5</v>
       </c>
       <c r="C21">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="D21">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="E21">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="F21">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="G21">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="H21">
         <v>5</v>
       </c>
       <c r="I21">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="J21">
         <v>5</v>
       </c>
       <c r="K21">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="L21">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="M21">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="N21">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="O21">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="P21">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="Q21">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="R21">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="S21">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="T21">
         <v>5</v>
       </c>
       <c r="U21">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="V21">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="W21">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="X21">
         <v>6</v>
       </c>
       <c r="Y21">
-        <v>7</v>
+        <v>5</v>
       </c>
     </row>
     <row r="22" spans="1:25">
@@ -2327,25 +2300,25 @@
         <v>5</v>
       </c>
       <c r="C22">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="D22">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="E22">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="F22">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="G22">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="H22">
         <v>5</v>
       </c>
       <c r="I22">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="J22">
         <v>5</v>
@@ -2357,25 +2330,25 @@
         <v>6</v>
       </c>
       <c r="M22">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="N22">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="O22">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="P22">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="Q22">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="R22">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="S22">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="T22">
         <v>5</v>
@@ -2387,13 +2360,13 @@
         <v>5</v>
       </c>
       <c r="W22">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="X22">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="Y22">
-        <v>5</v>
+        <v>7</v>
       </c>
     </row>
     <row r="23" spans="1:25">
@@ -2401,16 +2374,16 @@
         <v>31</v>
       </c>
       <c r="B23">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C23">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="D23">
         <v>5</v>
       </c>
       <c r="E23">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="F23">
         <v>5</v>
@@ -2419,55 +2392,55 @@
         <v>5</v>
       </c>
       <c r="H23">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="I23">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="J23">
         <v>5</v>
       </c>
       <c r="K23">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="L23">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="M23">
         <v>5</v>
       </c>
       <c r="N23">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="O23">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="P23">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="Q23">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="R23">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="S23">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="T23">
         <v>6</v>
       </c>
       <c r="U23">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="V23">
         <v>5</v>
       </c>
       <c r="W23">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="X23">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="Y23">
         <v>5</v>
@@ -2478,76 +2451,76 @@
         <v>32</v>
       </c>
       <c r="B24">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="C24">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="D24">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="E24">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="F24">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="G24">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="H24">
         <v>6</v>
       </c>
       <c r="I24">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="J24">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="K24">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="L24">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="M24">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="N24">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="O24">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="P24">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="Q24">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="R24">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="S24">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="T24">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="U24">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="V24">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="W24">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="X24">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="Y24">
-        <v>10</v>
+        <v>5</v>
       </c>
     </row>
     <row r="25" spans="1:25">
@@ -2555,16 +2528,16 @@
         <v>33</v>
       </c>
       <c r="B25">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="C25">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="D25">
         <v>6</v>
       </c>
       <c r="E25">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="F25">
         <v>8</v>
@@ -2573,7 +2546,7 @@
         <v>10</v>
       </c>
       <c r="H25">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="I25">
         <v>7</v>
@@ -2582,49 +2555,49 @@
         <v>8</v>
       </c>
       <c r="K25">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="L25">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="M25">
         <v>9</v>
       </c>
       <c r="N25">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="O25">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="P25">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="Q25">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="R25">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="S25">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="T25">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="U25">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="V25">
         <v>7</v>
       </c>
       <c r="W25">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="X25">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="Y25">
-        <v>10</v>
+        <v>9</v>
       </c>
     </row>
     <row r="26" spans="1:25">
@@ -2632,76 +2605,76 @@
         <v>34</v>
       </c>
       <c r="B26">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="C26">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="D26">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="E26">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="F26">
         <v>8</v>
       </c>
       <c r="G26">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="H26">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="I26">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="J26">
         <v>8</v>
       </c>
       <c r="K26">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="L26">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="M26">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="N26">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="O26">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="P26">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="Q26">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="R26">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="S26">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="T26">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="U26">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="V26">
         <v>8</v>
       </c>
       <c r="W26">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="X26">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="Y26">
-        <v>7</v>
+        <v>10</v>
       </c>
     </row>
     <row r="27" spans="1:25">
@@ -2709,76 +2682,76 @@
         <v>35</v>
       </c>
       <c r="B27">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C27">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="D27">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="E27">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="F27">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="G27">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="H27">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="I27">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="J27">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="K27">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="L27">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="M27">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="N27">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="O27">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="P27">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="Q27">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="R27">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="S27">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="T27">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="U27">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="V27">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="W27">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="X27">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="Y27">
-        <v>10</v>
+        <v>7</v>
       </c>
     </row>
     <row r="28" spans="1:25">
@@ -2786,7 +2759,7 @@
         <v>36</v>
       </c>
       <c r="B28">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="C28">
         <v>9</v>
@@ -2795,7 +2768,7 @@
         <v>9</v>
       </c>
       <c r="E28">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="F28">
         <v>9</v>
@@ -2804,58 +2777,58 @@
         <v>9</v>
       </c>
       <c r="H28">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="I28">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="J28">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="K28">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="L28">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="M28">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="N28">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="O28">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="P28">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="Q28">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R28">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="S28">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="T28">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="U28">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="V28">
         <v>9</v>
       </c>
       <c r="W28">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="X28">
         <v>9</v>
       </c>
       <c r="Y28">
-        <v>9</v>
+        <v>10</v>
       </c>
     </row>
     <row r="29" spans="1:25">
@@ -2866,19 +2839,19 @@
         <v>6</v>
       </c>
       <c r="C29">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="D29">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="E29">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="F29">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="G29">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="H29">
         <v>6</v>
@@ -2887,34 +2860,34 @@
         <v>7</v>
       </c>
       <c r="J29">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="K29">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="L29">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="M29">
         <v>9</v>
       </c>
       <c r="N29">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="O29">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="P29">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="Q29">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="R29">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="S29">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="T29">
         <v>6</v>
@@ -2923,16 +2896,16 @@
         <v>8</v>
       </c>
       <c r="V29">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="W29">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="X29">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="Y29">
-        <v>10</v>
+        <v>9</v>
       </c>
     </row>
     <row r="30" spans="1:25">
@@ -2940,73 +2913,73 @@
         <v>38</v>
       </c>
       <c r="B30">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="C30">
         <v>8</v>
       </c>
       <c r="D30">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="E30">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="F30">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="G30">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="H30">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="I30">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="J30">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="K30">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="L30">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="M30">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="N30">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="O30">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="P30">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="Q30">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="R30">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="S30">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="T30">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="U30">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="V30">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="W30">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="X30">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="Y30">
         <v>10</v>
@@ -3017,73 +2990,73 @@
         <v>39</v>
       </c>
       <c r="B31">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="C31">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="D31">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="E31">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="F31">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="G31">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="H31">
         <v>8</v>
       </c>
       <c r="I31">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="J31">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="K31">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="L31">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="M31">
         <v>10</v>
       </c>
       <c r="N31">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="O31">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="P31">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="Q31">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="R31">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="S31">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="T31">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="U31">
         <v>8</v>
       </c>
       <c r="V31">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="W31">
         <v>9</v>
       </c>
       <c r="X31">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="Y31">
         <v>10</v>
@@ -3094,76 +3067,76 @@
         <v>40</v>
       </c>
       <c r="B32">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="C32">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="D32">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="E32">
         <v>8</v>
       </c>
       <c r="F32">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="G32">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="H32">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="I32">
         <v>6</v>
       </c>
       <c r="J32">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="K32">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="L32">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="M32">
         <v>10</v>
       </c>
       <c r="N32">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="O32">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="P32">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="Q32">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R32">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="S32">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="T32">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="U32">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="V32">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="W32">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="X32">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="Y32">
-        <v>8</v>
+        <v>10</v>
       </c>
     </row>
     <row r="33" spans="1:25">
@@ -3171,76 +3144,76 @@
         <v>41</v>
       </c>
       <c r="B33">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="C33">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="D33">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="E33">
         <v>8</v>
       </c>
       <c r="F33">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="G33">
         <v>5</v>
       </c>
       <c r="H33">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="I33">
         <v>6</v>
       </c>
       <c r="J33">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="K33">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="L33">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="M33">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="N33">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="O33">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="P33">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="Q33">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="R33">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="S33">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="T33">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="U33">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="V33">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="W33">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="X33">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="Y33">
-        <v>5</v>
+        <v>7</v>
       </c>
     </row>
     <row r="34" spans="1:25">
@@ -3248,76 +3221,153 @@
         <v>42</v>
       </c>
       <c r="B34">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="C34">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="D34">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="E34">
         <v>8</v>
       </c>
       <c r="F34">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="G34">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="H34">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="I34">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="J34">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="K34">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="L34">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="M34">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="N34">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="O34">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="P34">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="Q34">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="R34">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="S34">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="T34">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="U34">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="V34">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="W34">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="X34">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="Y34">
-        <v>10</v>
+        <v>6</v>
+      </c>
+    </row>
+    <row r="35" spans="1:25">
+      <c r="A35" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="B35">
+        <v>8</v>
+      </c>
+      <c r="C35">
+        <v>10</v>
+      </c>
+      <c r="D35">
+        <v>9</v>
+      </c>
+      <c r="E35">
+        <v>8</v>
+      </c>
+      <c r="F35">
+        <v>9</v>
+      </c>
+      <c r="G35">
+        <v>9</v>
+      </c>
+      <c r="H35">
+        <v>7</v>
+      </c>
+      <c r="I35">
+        <v>9</v>
+      </c>
+      <c r="J35">
+        <v>9</v>
+      </c>
+      <c r="K35">
+        <v>9</v>
+      </c>
+      <c r="L35">
+        <v>8</v>
+      </c>
+      <c r="M35">
+        <v>10</v>
+      </c>
+      <c r="N35">
+        <v>8</v>
+      </c>
+      <c r="O35">
+        <v>8</v>
+      </c>
+      <c r="P35">
+        <v>5</v>
+      </c>
+      <c r="Q35">
+        <v>10</v>
+      </c>
+      <c r="R35">
+        <v>9</v>
+      </c>
+      <c r="S35">
+        <v>8</v>
+      </c>
+      <c r="T35">
+        <v>8</v>
+      </c>
+      <c r="U35">
+        <v>9</v>
+      </c>
+      <c r="V35">
+        <v>8</v>
+      </c>
+      <c r="W35">
+        <v>9</v>
+      </c>
+      <c r="X35">
+        <v>9</v>
+      </c>
+      <c r="Y35">
+        <v>9</v>
       </c>
     </row>
   </sheetData>
@@ -3344,31 +3394,31 @@
         <v>0</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="H1" s="1" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="I1" s="1" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="J1" s="1" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
     </row>
     <row r="2" spans="1:10">
@@ -3376,25 +3426,25 @@
         <v>7</v>
       </c>
       <c r="B2" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="C2">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="D2">
-        <v>18</v>
+        <v>24</v>
       </c>
       <c r="E2">
-        <v>13</v>
+        <v>8</v>
       </c>
       <c r="F2">
-        <v>58.06</v>
+        <v>75</v>
       </c>
       <c r="G2">
-        <v>41.94</v>
+        <v>25</v>
       </c>
       <c r="H2">
-        <v>6.6</v>
+        <v>6.5</v>
       </c>
       <c r="I2">
         <v>0</v>
@@ -3405,28 +3455,28 @@
     </row>
     <row r="3" spans="1:10">
       <c r="A3" t="s">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="B3" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="C3">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="D3">
-        <v>20</v>
+        <v>26</v>
       </c>
       <c r="E3">
-        <v>11</v>
+        <v>6</v>
       </c>
       <c r="F3">
-        <v>64.52</v>
+        <v>81.25</v>
       </c>
       <c r="G3">
-        <v>35.48</v>
+        <v>18.75</v>
       </c>
       <c r="H3">
-        <v>6.6</v>
+        <v>7.5</v>
       </c>
       <c r="I3">
         <v>0</v>
@@ -3437,60 +3487,60 @@
     </row>
     <row r="4" spans="1:10">
       <c r="A4" t="s">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="B4" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="C4">
         <v>31</v>
       </c>
       <c r="D4">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="E4">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="F4">
-        <v>74.19</v>
+        <v>83.87</v>
       </c>
       <c r="G4">
-        <v>0</v>
+        <v>16.13</v>
       </c>
       <c r="H4">
-        <v>8.1</v>
+        <v>6.7</v>
       </c>
       <c r="I4">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="J4">
-        <v>25.81</v>
+        <v>0</v>
       </c>
     </row>
     <row r="5" spans="1:10">
       <c r="A5" t="s">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="B5" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="C5">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="D5">
-        <v>23</v>
+        <v>28</v>
       </c>
       <c r="E5">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="F5">
-        <v>74.19</v>
+        <v>87.5</v>
       </c>
       <c r="G5">
-        <v>25.81</v>
+        <v>12.5</v>
       </c>
       <c r="H5">
-        <v>7.7</v>
+        <v>6.7</v>
       </c>
       <c r="I5">
         <v>0</v>
@@ -3501,28 +3551,28 @@
     </row>
     <row r="6" spans="1:10">
       <c r="A6" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="B6" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="C6">
         <v>31</v>
       </c>
       <c r="D6">
-        <v>24</v>
+        <v>28</v>
       </c>
       <c r="E6">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="F6">
-        <v>77.42</v>
+        <v>90.31999999999999</v>
       </c>
       <c r="G6">
-        <v>22.58</v>
+        <v>9.68</v>
       </c>
       <c r="H6">
-        <v>7</v>
+        <v>7.2</v>
       </c>
       <c r="I6">
         <v>0</v>
@@ -3533,34 +3583,34 @@
     </row>
     <row r="7" spans="1:10">
       <c r="A7" t="s">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="B7" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="C7">
         <v>31</v>
       </c>
       <c r="D7">
-        <v>27</v>
+        <v>30</v>
       </c>
       <c r="E7">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F7">
-        <v>87.09999999999999</v>
+        <v>96.77</v>
       </c>
       <c r="G7">
-        <v>0</v>
+        <v>3.23</v>
       </c>
       <c r="H7">
-        <v>7.1</v>
+        <v>7</v>
       </c>
       <c r="I7">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="J7">
-        <v>12.9</v>
+        <v>0</v>
       </c>
     </row>
   </sheetData>
@@ -3570,7 +3620,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:F13"/>
+  <dimension ref="A1:F1"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="30.7109375" customWidth="1"/>
@@ -3579,262 +3629,22 @@
   <sheetData>
     <row r="1" spans="1:6">
       <c r="A1" s="1" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="E1" s="1" t="s">
         <v>0</v>
       </c>
       <c r="F1" s="1" t="s">
         <v>11</v>
-      </c>
-    </row>
-    <row r="2" spans="1:6">
-      <c r="A2">
-        <v>21330051920186</v>
-      </c>
-      <c r="B2" t="s">
-        <v>62</v>
-      </c>
-      <c r="C2" t="s">
-        <v>65</v>
-      </c>
-      <c r="D2" t="s">
-        <v>79</v>
-      </c>
-      <c r="E2" t="s">
-        <v>8</v>
-      </c>
-      <c r="F2" t="s">
-        <v>54</v>
-      </c>
-    </row>
-    <row r="3" spans="1:6">
-      <c r="A3">
-        <v>21330051920186</v>
-      </c>
-      <c r="B3" t="s">
-        <v>62</v>
-      </c>
-      <c r="C3" t="s">
-        <v>65</v>
-      </c>
-      <c r="D3" t="s">
-        <v>79</v>
-      </c>
-      <c r="E3" t="s">
-        <v>6</v>
-      </c>
-      <c r="F3" t="s">
-        <v>57</v>
-      </c>
-    </row>
-    <row r="4" spans="1:6">
-      <c r="A4">
-        <v>21330051920189</v>
-      </c>
-      <c r="B4" t="s">
-        <v>63</v>
-      </c>
-      <c r="C4" t="s">
-        <v>71</v>
-      </c>
-      <c r="D4" t="s">
-        <v>80</v>
-      </c>
-      <c r="E4" t="s">
-        <v>6</v>
-      </c>
-      <c r="F4" t="s">
-        <v>57</v>
-      </c>
-    </row>
-    <row r="5" spans="1:6">
-      <c r="A5">
-        <v>21330051920190</v>
-      </c>
-      <c r="B5" t="s">
-        <v>64</v>
-      </c>
-      <c r="C5" t="s">
-        <v>72</v>
-      </c>
-      <c r="D5" t="s">
-        <v>81</v>
-      </c>
-      <c r="E5" t="s">
-        <v>8</v>
-      </c>
-      <c r="F5" t="s">
-        <v>54</v>
-      </c>
-    </row>
-    <row r="6" spans="1:6">
-      <c r="A6">
-        <v>21330051920195</v>
-      </c>
-      <c r="B6" t="s">
-        <v>65</v>
-      </c>
-      <c r="C6" t="s">
-        <v>73</v>
-      </c>
-      <c r="D6" t="s">
-        <v>82</v>
-      </c>
-      <c r="E6" t="s">
-        <v>8</v>
-      </c>
-      <c r="F6" t="s">
-        <v>54</v>
-      </c>
-    </row>
-    <row r="7" spans="1:6">
-      <c r="A7">
-        <v>21330051920198</v>
-      </c>
-      <c r="B7" t="s">
-        <v>66</v>
-      </c>
-      <c r="C7" t="s">
-        <v>74</v>
-      </c>
-      <c r="D7" t="s">
-        <v>83</v>
-      </c>
-      <c r="E7" t="s">
-        <v>8</v>
-      </c>
-      <c r="F7" t="s">
-        <v>54</v>
-      </c>
-    </row>
-    <row r="8" spans="1:6">
-      <c r="A8">
-        <v>21330051920199</v>
-      </c>
-      <c r="B8" t="s">
-        <v>67</v>
-      </c>
-      <c r="C8" t="s">
-        <v>75</v>
-      </c>
-      <c r="D8" t="s">
-        <v>84</v>
-      </c>
-      <c r="E8" t="s">
-        <v>8</v>
-      </c>
-      <c r="F8" t="s">
-        <v>54</v>
-      </c>
-    </row>
-    <row r="9" spans="1:6">
-      <c r="A9">
-        <v>21330051920200</v>
-      </c>
-      <c r="B9" t="s">
-        <v>68</v>
-      </c>
-      <c r="C9" t="s">
-        <v>76</v>
-      </c>
-      <c r="D9" t="s">
-        <v>85</v>
-      </c>
-      <c r="E9" t="s">
-        <v>8</v>
-      </c>
-      <c r="F9" t="s">
-        <v>54</v>
-      </c>
-    </row>
-    <row r="10" spans="1:6">
-      <c r="A10">
-        <v>21330051920200</v>
-      </c>
-      <c r="B10" t="s">
-        <v>68</v>
-      </c>
-      <c r="C10" t="s">
-        <v>76</v>
-      </c>
-      <c r="D10" t="s">
-        <v>85</v>
-      </c>
-      <c r="E10" t="s">
-        <v>6</v>
-      </c>
-      <c r="F10" t="s">
-        <v>57</v>
-      </c>
-    </row>
-    <row r="11" spans="1:6">
-      <c r="A11">
-        <v>21330051920201</v>
-      </c>
-      <c r="B11" t="s">
-        <v>69</v>
-      </c>
-      <c r="C11" t="s">
-        <v>77</v>
-      </c>
-      <c r="D11" t="s">
-        <v>86</v>
-      </c>
-      <c r="E11" t="s">
-        <v>8</v>
-      </c>
-      <c r="F11" t="s">
-        <v>54</v>
-      </c>
-    </row>
-    <row r="12" spans="1:6">
-      <c r="A12">
-        <v>21330051920203</v>
-      </c>
-      <c r="B12" t="s">
-        <v>70</v>
-      </c>
-      <c r="C12" t="s">
-        <v>78</v>
-      </c>
-      <c r="D12" t="s">
-        <v>87</v>
-      </c>
-      <c r="E12" t="s">
-        <v>8</v>
-      </c>
-      <c r="F12" t="s">
-        <v>54</v>
-      </c>
-    </row>
-    <row r="13" spans="1:6">
-      <c r="A13">
-        <v>21330051920203</v>
-      </c>
-      <c r="B13" t="s">
-        <v>70</v>
-      </c>
-      <c r="C13" t="s">
-        <v>78</v>
-      </c>
-      <c r="D13" t="s">
-        <v>87</v>
-      </c>
-      <c r="E13" t="s">
-        <v>6</v>
-      </c>
-      <c r="F13" t="s">
-        <v>57</v>
       </c>
     </row>
   </sheetData>
@@ -3844,7 +3654,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:E32"/>
+  <dimension ref="A1:E33"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="30.7109375" customWidth="1"/>
@@ -3853,186 +3663,186 @@
   <sheetData>
     <row r="1" spans="1:5">
       <c r="A1" s="1" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
     </row>
     <row r="2" spans="1:5">
       <c r="A2">
-        <v>21330051920186</v>
+        <v>21330051920185</v>
       </c>
       <c r="B2" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="C2" t="s">
-        <v>65</v>
+        <v>92</v>
       </c>
       <c r="D2" t="s">
-        <v>79</v>
+        <v>116</v>
       </c>
       <c r="E2">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="3" spans="1:5">
       <c r="A3">
-        <v>21330051920200</v>
+        <v>21330051920186</v>
       </c>
       <c r="B3" t="s">
-        <v>68</v>
+        <v>63</v>
       </c>
       <c r="C3" t="s">
-        <v>76</v>
+        <v>71</v>
       </c>
       <c r="D3" t="s">
-        <v>85</v>
+        <v>117</v>
       </c>
       <c r="E3">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="4" spans="1:5">
       <c r="A4">
-        <v>21330051920203</v>
+        <v>21330051920187</v>
       </c>
       <c r="B4" t="s">
-        <v>70</v>
+        <v>64</v>
       </c>
       <c r="C4" t="s">
-        <v>78</v>
+        <v>93</v>
       </c>
       <c r="D4" t="s">
-        <v>87</v>
+        <v>118</v>
       </c>
       <c r="E4">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="5" spans="1:5">
       <c r="A5">
-        <v>21330051920189</v>
+        <v>21330051920188</v>
       </c>
       <c r="B5" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="C5" t="s">
-        <v>71</v>
+        <v>94</v>
       </c>
       <c r="D5" t="s">
-        <v>80</v>
+        <v>119</v>
       </c>
       <c r="E5">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="6" spans="1:5">
       <c r="A6">
-        <v>21330051920190</v>
+        <v>21330051920189</v>
       </c>
       <c r="B6" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="C6" t="s">
-        <v>72</v>
+        <v>95</v>
       </c>
       <c r="D6" t="s">
-        <v>81</v>
+        <v>120</v>
       </c>
       <c r="E6">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="7" spans="1:5">
       <c r="A7">
-        <v>21330051920195</v>
+        <v>21330051920190</v>
       </c>
       <c r="B7" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="C7" t="s">
-        <v>73</v>
+        <v>96</v>
       </c>
       <c r="D7" t="s">
-        <v>82</v>
+        <v>121</v>
       </c>
       <c r="E7">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="8" spans="1:5">
       <c r="A8">
-        <v>21330051920198</v>
+        <v>21330051920191</v>
       </c>
       <c r="B8" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="C8" t="s">
-        <v>74</v>
+        <v>97</v>
       </c>
       <c r="D8" t="s">
-        <v>83</v>
+        <v>122</v>
       </c>
       <c r="E8">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="9" spans="1:5">
       <c r="A9">
-        <v>21330051920199</v>
+        <v>21330051920192</v>
       </c>
       <c r="B9" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="C9" t="s">
-        <v>75</v>
+        <v>82</v>
       </c>
       <c r="D9" t="s">
-        <v>84</v>
+        <v>123</v>
       </c>
       <c r="E9">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="10" spans="1:5">
       <c r="A10">
-        <v>21330051920201</v>
+        <v>21330051920193</v>
       </c>
       <c r="B10" t="s">
         <v>69</v>
       </c>
       <c r="C10" t="s">
-        <v>77</v>
+        <v>98</v>
       </c>
       <c r="D10" t="s">
-        <v>86</v>
+        <v>124</v>
       </c>
       <c r="E10">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="11" spans="1:5">
       <c r="A11">
-        <v>21330051920185</v>
+        <v>19330061430023</v>
       </c>
       <c r="B11" t="s">
-        <v>62</v>
+        <v>69</v>
       </c>
       <c r="C11" t="s">
-        <v>106</v>
+        <v>99</v>
       </c>
       <c r="D11" t="s">
-        <v>123</v>
+        <v>125</v>
       </c>
       <c r="E11">
         <v>0</v>
@@ -4040,16 +3850,16 @@
     </row>
     <row r="12" spans="1:5">
       <c r="A12">
-        <v>21330051920187</v>
+        <v>21330051920194</v>
       </c>
       <c r="B12" t="s">
-        <v>88</v>
+        <v>70</v>
       </c>
       <c r="C12" t="s">
-        <v>107</v>
+        <v>100</v>
       </c>
       <c r="D12" t="s">
-        <v>124</v>
+        <v>126</v>
       </c>
       <c r="E12">
         <v>0</v>
@@ -4057,16 +3867,16 @@
     </row>
     <row r="13" spans="1:5">
       <c r="A13">
-        <v>21330051920188</v>
+        <v>21330051920195</v>
       </c>
       <c r="B13" t="s">
-        <v>88</v>
+        <v>71</v>
       </c>
       <c r="C13" t="s">
-        <v>108</v>
+        <v>101</v>
       </c>
       <c r="D13" t="s">
-        <v>125</v>
+        <v>127</v>
       </c>
       <c r="E13">
         <v>0</v>
@@ -4074,16 +3884,16 @@
     </row>
     <row r="14" spans="1:5">
       <c r="A14">
-        <v>21330051920191</v>
+        <v>21330051920196</v>
       </c>
       <c r="B14" t="s">
-        <v>89</v>
+        <v>72</v>
       </c>
       <c r="C14" t="s">
-        <v>109</v>
+        <v>91</v>
       </c>
       <c r="D14" t="s">
-        <v>126</v>
+        <v>128</v>
       </c>
       <c r="E14">
         <v>0</v>
@@ -4091,16 +3901,16 @@
     </row>
     <row r="15" spans="1:5">
       <c r="A15">
-        <v>21330051920192</v>
+        <v>21330051920197</v>
       </c>
       <c r="B15" t="s">
-        <v>90</v>
+        <v>73</v>
       </c>
       <c r="C15" t="s">
-        <v>97</v>
+        <v>102</v>
       </c>
       <c r="D15" t="s">
-        <v>127</v>
+        <v>129</v>
       </c>
       <c r="E15">
         <v>0</v>
@@ -4108,16 +3918,16 @@
     </row>
     <row r="16" spans="1:5">
       <c r="A16">
-        <v>21330051920193</v>
+        <v>21330051920386</v>
       </c>
       <c r="B16" t="s">
-        <v>91</v>
+        <v>74</v>
       </c>
       <c r="C16" t="s">
-        <v>110</v>
+        <v>103</v>
       </c>
       <c r="D16" t="s">
-        <v>128</v>
+        <v>130</v>
       </c>
       <c r="E16">
         <v>0</v>
@@ -4125,16 +3935,16 @@
     </row>
     <row r="17" spans="1:5">
       <c r="A17">
-        <v>21330051920194</v>
+        <v>21330051920198</v>
       </c>
       <c r="B17" t="s">
-        <v>92</v>
+        <v>75</v>
       </c>
       <c r="C17" t="s">
-        <v>111</v>
+        <v>88</v>
       </c>
       <c r="D17" t="s">
-        <v>129</v>
+        <v>131</v>
       </c>
       <c r="E17">
         <v>0</v>
@@ -4142,16 +3952,16 @@
     </row>
     <row r="18" spans="1:5">
       <c r="A18">
-        <v>21330051920196</v>
+        <v>21330051920199</v>
       </c>
       <c r="B18" t="s">
-        <v>93</v>
+        <v>76</v>
       </c>
       <c r="C18" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="D18" t="s">
-        <v>130</v>
+        <v>132</v>
       </c>
       <c r="E18">
         <v>0</v>
@@ -4159,16 +3969,16 @@
     </row>
     <row r="19" spans="1:5">
       <c r="A19">
-        <v>21330051920197</v>
+        <v>21330051920200</v>
       </c>
       <c r="B19" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="C19" t="s">
-        <v>112</v>
+        <v>73</v>
       </c>
       <c r="D19" t="s">
-        <v>131</v>
+        <v>133</v>
       </c>
       <c r="E19">
         <v>0</v>
@@ -4176,16 +3986,16 @@
     </row>
     <row r="20" spans="1:5">
       <c r="A20">
-        <v>21330051920386</v>
+        <v>21330051920201</v>
       </c>
       <c r="B20" t="s">
-        <v>94</v>
+        <v>78</v>
       </c>
       <c r="C20" t="s">
-        <v>113</v>
+        <v>105</v>
       </c>
       <c r="D20" t="s">
-        <v>132</v>
+        <v>134</v>
       </c>
       <c r="E20">
         <v>0</v>
@@ -4196,13 +4006,13 @@
         <v>21330051920202</v>
       </c>
       <c r="B21" t="s">
-        <v>95</v>
+        <v>79</v>
       </c>
       <c r="C21" t="s">
-        <v>114</v>
+        <v>106</v>
       </c>
       <c r="D21" t="s">
-        <v>133</v>
+        <v>135</v>
       </c>
       <c r="E21">
         <v>0</v>
@@ -4210,16 +4020,16 @@
     </row>
     <row r="22" spans="1:5">
       <c r="A22">
-        <v>21330051920204</v>
+        <v>21330051920203</v>
       </c>
       <c r="B22" t="s">
-        <v>96</v>
+        <v>80</v>
       </c>
       <c r="C22" t="s">
-        <v>115</v>
+        <v>107</v>
       </c>
       <c r="D22" t="s">
-        <v>134</v>
+        <v>136</v>
       </c>
       <c r="E22">
         <v>0</v>
@@ -4227,16 +4037,16 @@
     </row>
     <row r="23" spans="1:5">
       <c r="A23">
-        <v>21330051920205</v>
+        <v>21330051920204</v>
       </c>
       <c r="B23" t="s">
-        <v>97</v>
+        <v>81</v>
       </c>
       <c r="C23" t="s">
-        <v>116</v>
+        <v>108</v>
       </c>
       <c r="D23" t="s">
-        <v>135</v>
+        <v>137</v>
       </c>
       <c r="E23">
         <v>0</v>
@@ -4244,16 +4054,16 @@
     </row>
     <row r="24" spans="1:5">
       <c r="A24">
-        <v>21330051920206</v>
+        <v>21330051920205</v>
       </c>
       <c r="B24" t="s">
-        <v>98</v>
+        <v>82</v>
       </c>
       <c r="C24" t="s">
-        <v>117</v>
+        <v>109</v>
       </c>
       <c r="D24" t="s">
-        <v>136</v>
+        <v>138</v>
       </c>
       <c r="E24">
         <v>0</v>
@@ -4261,16 +4071,16 @@
     </row>
     <row r="25" spans="1:5">
       <c r="A25">
-        <v>21330051920207</v>
+        <v>21330051920206</v>
       </c>
       <c r="B25" t="s">
-        <v>99</v>
+        <v>83</v>
       </c>
       <c r="C25" t="s">
-        <v>102</v>
+        <v>110</v>
       </c>
       <c r="D25" t="s">
-        <v>137</v>
+        <v>139</v>
       </c>
       <c r="E25">
         <v>0</v>
@@ -4278,16 +4088,16 @@
     </row>
     <row r="26" spans="1:5">
       <c r="A26">
-        <v>21330051920208</v>
+        <v>21330051920207</v>
       </c>
       <c r="B26" t="s">
-        <v>100</v>
+        <v>84</v>
       </c>
       <c r="C26" t="s">
-        <v>71</v>
+        <v>87</v>
       </c>
       <c r="D26" t="s">
-        <v>138</v>
+        <v>140</v>
       </c>
       <c r="E26">
         <v>0</v>
@@ -4295,16 +4105,16 @@
     </row>
     <row r="27" spans="1:5">
       <c r="A27">
-        <v>21330051920209</v>
+        <v>21330051920208</v>
       </c>
       <c r="B27" t="s">
-        <v>101</v>
+        <v>85</v>
       </c>
       <c r="C27" t="s">
-        <v>118</v>
+        <v>95</v>
       </c>
       <c r="D27" t="s">
-        <v>139</v>
+        <v>141</v>
       </c>
       <c r="E27">
         <v>0</v>
@@ -4312,16 +4122,16 @@
     </row>
     <row r="28" spans="1:5">
       <c r="A28">
-        <v>21330051920210</v>
+        <v>21330051920209</v>
       </c>
       <c r="B28" t="s">
-        <v>102</v>
+        <v>86</v>
       </c>
       <c r="C28" t="s">
-        <v>119</v>
+        <v>111</v>
       </c>
       <c r="D28" t="s">
-        <v>140</v>
+        <v>142</v>
       </c>
       <c r="E28">
         <v>0</v>
@@ -4329,16 +4139,16 @@
     </row>
     <row r="29" spans="1:5">
       <c r="A29">
-        <v>21330051920211</v>
+        <v>21330051920210</v>
       </c>
       <c r="B29" t="s">
-        <v>74</v>
+        <v>87</v>
       </c>
       <c r="C29" t="s">
-        <v>109</v>
+        <v>112</v>
       </c>
       <c r="D29" t="s">
-        <v>141</v>
+        <v>143</v>
       </c>
       <c r="E29">
         <v>0</v>
@@ -4346,16 +4156,16 @@
     </row>
     <row r="30" spans="1:5">
       <c r="A30">
-        <v>21330051920212</v>
+        <v>21330051920211</v>
       </c>
       <c r="B30" t="s">
-        <v>103</v>
+        <v>88</v>
       </c>
       <c r="C30" t="s">
-        <v>120</v>
+        <v>97</v>
       </c>
       <c r="D30" t="s">
-        <v>142</v>
+        <v>144</v>
       </c>
       <c r="E30">
         <v>0</v>
@@ -4363,16 +4173,16 @@
     </row>
     <row r="31" spans="1:5">
       <c r="A31">
-        <v>21330051920213</v>
+        <v>21330051920212</v>
       </c>
       <c r="B31" t="s">
-        <v>104</v>
+        <v>89</v>
       </c>
       <c r="C31" t="s">
-        <v>121</v>
+        <v>113</v>
       </c>
       <c r="D31" t="s">
-        <v>143</v>
+        <v>145</v>
       </c>
       <c r="E31">
         <v>0</v>
@@ -4380,18 +4190,35 @@
     </row>
     <row r="32" spans="1:5">
       <c r="A32">
+        <v>21330051920213</v>
+      </c>
+      <c r="B32" t="s">
+        <v>90</v>
+      </c>
+      <c r="C32" t="s">
+        <v>114</v>
+      </c>
+      <c r="D32" t="s">
+        <v>146</v>
+      </c>
+      <c r="E32">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="33" spans="1:5">
+      <c r="A33">
         <v>21330051920214</v>
       </c>
-      <c r="B32" t="s">
-        <v>105</v>
-      </c>
-      <c r="C32" t="s">
-        <v>122</v>
-      </c>
-      <c r="D32" t="s">
-        <v>144</v>
-      </c>
-      <c r="E32">
+      <c r="B33" t="s">
+        <v>91</v>
+      </c>
+      <c r="C33" t="s">
+        <v>115</v>
+      </c>
+      <c r="D33" t="s">
+        <v>147</v>
+      </c>
+      <c r="E33">
         <v>0</v>
       </c>
     </row>
@@ -4402,7 +4229,7 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G11"/>
+  <dimension ref="A1:G7"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="30.7109375" customWidth="1"/>
@@ -4411,22 +4238,22 @@
   <sheetData>
     <row r="1" spans="1:7">
       <c r="A1" s="1" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="E1" s="1" t="s">
         <v>0</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="G1" s="1" t="s">
         <v>4</v>
@@ -4434,22 +4261,22 @@
     </row>
     <row r="2" spans="1:7">
       <c r="A2">
-        <v>21330051920197</v>
+        <v>21330051920201</v>
       </c>
       <c r="B2" t="s">
-        <v>76</v>
+        <v>78</v>
       </c>
       <c r="C2" t="s">
-        <v>112</v>
+        <v>105</v>
       </c>
       <c r="D2" t="s">
-        <v>131</v>
+        <v>134</v>
       </c>
       <c r="E2" t="s">
         <v>5</v>
       </c>
       <c r="F2" t="s">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="G2">
         <v>5</v>
@@ -4457,22 +4284,22 @@
     </row>
     <row r="3" spans="1:7">
       <c r="A3">
-        <v>21330051920197</v>
+        <v>21330051920201</v>
       </c>
       <c r="B3" t="s">
-        <v>76</v>
+        <v>78</v>
       </c>
       <c r="C3" t="s">
-        <v>112</v>
+        <v>105</v>
       </c>
       <c r="D3" t="s">
-        <v>131</v>
+        <v>134</v>
       </c>
       <c r="E3" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="F3" t="s">
-        <v>56</v>
+        <v>53</v>
       </c>
       <c r="G3">
         <v>5</v>
@@ -4480,19 +4307,19 @@
     </row>
     <row r="4" spans="1:7">
       <c r="A4">
-        <v>21330051920386</v>
+        <v>21330051920202</v>
       </c>
       <c r="B4" t="s">
-        <v>94</v>
+        <v>79</v>
       </c>
       <c r="C4" t="s">
-        <v>113</v>
+        <v>106</v>
       </c>
       <c r="D4" t="s">
-        <v>132</v>
+        <v>135</v>
       </c>
       <c r="E4" t="s">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="F4" t="s">
         <v>53</v>
@@ -4503,22 +4330,22 @@
     </row>
     <row r="5" spans="1:7">
       <c r="A5">
-        <v>21330051920386</v>
+        <v>21330051920202</v>
       </c>
       <c r="B5" t="s">
-        <v>94</v>
+        <v>79</v>
       </c>
       <c r="C5" t="s">
-        <v>113</v>
+        <v>106</v>
       </c>
       <c r="D5" t="s">
-        <v>132</v>
+        <v>135</v>
       </c>
       <c r="E5" t="s">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="F5" t="s">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="G5">
         <v>5</v>
@@ -4526,22 +4353,22 @@
     </row>
     <row r="6" spans="1:7">
       <c r="A6">
-        <v>21330051920201</v>
+        <v>21330051920188</v>
       </c>
       <c r="B6" t="s">
-        <v>69</v>
+        <v>64</v>
       </c>
       <c r="C6" t="s">
-        <v>77</v>
+        <v>94</v>
       </c>
       <c r="D6" t="s">
-        <v>86</v>
+        <v>119</v>
       </c>
       <c r="E6" t="s">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="F6" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="G6">
         <v>5</v>
@@ -4549,116 +4376,24 @@
     </row>
     <row r="7" spans="1:7">
       <c r="A7">
-        <v>21330051920201</v>
+        <v>19330061430023</v>
       </c>
       <c r="B7" t="s">
         <v>69</v>
       </c>
       <c r="C7" t="s">
-        <v>77</v>
+        <v>99</v>
       </c>
       <c r="D7" t="s">
-        <v>86</v>
+        <v>125</v>
       </c>
       <c r="E7" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="F7" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="G7">
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="8" spans="1:7">
-      <c r="A8">
-        <v>21330051920192</v>
-      </c>
-      <c r="B8" t="s">
-        <v>90</v>
-      </c>
-      <c r="C8" t="s">
-        <v>97</v>
-      </c>
-      <c r="D8" t="s">
-        <v>127</v>
-      </c>
-      <c r="E8" t="s">
-        <v>7</v>
-      </c>
-      <c r="F8" t="s">
-        <v>52</v>
-      </c>
-      <c r="G8">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="9" spans="1:7">
-      <c r="A9">
-        <v>21330051920199</v>
-      </c>
-      <c r="B9" t="s">
-        <v>67</v>
-      </c>
-      <c r="C9" t="s">
-        <v>75</v>
-      </c>
-      <c r="D9" t="s">
-        <v>84</v>
-      </c>
-      <c r="E9" t="s">
-        <v>8</v>
-      </c>
-      <c r="F9" t="s">
-        <v>54</v>
-      </c>
-      <c r="G9">
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="10" spans="1:7">
-      <c r="A10">
-        <v>21330051920209</v>
-      </c>
-      <c r="B10" t="s">
-        <v>101</v>
-      </c>
-      <c r="C10" t="s">
-        <v>118</v>
-      </c>
-      <c r="D10" t="s">
-        <v>139</v>
-      </c>
-      <c r="E10" t="s">
-        <v>7</v>
-      </c>
-      <c r="F10" t="s">
-        <v>52</v>
-      </c>
-      <c r="G10">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="11" spans="1:7">
-      <c r="A11">
-        <v>21330051920212</v>
-      </c>
-      <c r="B11" t="s">
-        <v>103</v>
-      </c>
-      <c r="C11" t="s">
-        <v>120</v>
-      </c>
-      <c r="D11" t="s">
-        <v>142</v>
-      </c>
-      <c r="E11" t="s">
-        <v>7</v>
-      </c>
-      <c r="F11" t="s">
-        <v>52</v>
-      </c>
-      <c r="G11">
         <v>5</v>
       </c>
     </row>
